--- a/Pm Số liệu điều hành bay - Kiểm thử theo Bảng 1.xlsx
+++ b/Pm Số liệu điều hành bay - Kiểm thử theo Bảng 1.xlsx
@@ -1,69 +1,25 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel</Application>
-  <DocSecurity>0</DocSecurity>
-  <ScaleCrop>false</ScaleCrop>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Worksheets</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>1</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="1" baseType="lpstr">
-      <vt:lpstr>Trang tính1</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <AppVersion>15.0300</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2026\QLB\TrienKhai\ATFM_WEB\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Trang tính1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="152511"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <cp:lastModifiedBy>NGOQUY</cp:lastModifiedBy>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-09-04T08:43:51Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\calcChain.xml><?xml version="1.0" encoding="utf-8"?>
-<calcChain xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <c r="K3" i="1" l="1"/>
-  <c r="J3" i="1" s="1"/>
-  <c r="H3" i="1"/>
-  <c r="G3" i="1"/>
-  <c r="F3" i="1"/>
-  <c r="E3" i="1"/>
-  <c r="D3" i="1"/>
-  <c r="I3" i="1" s="1"/>
-  <c r="O2" i="1"/>
-  <c r="N2" i="1"/>
-  <c r="M2" i="1"/>
-  <c r="L2" i="1"/>
-  <c r="K2" i="1"/>
-  <c r="J2" i="1" s="1"/>
-  <c r="H2" i="1"/>
-  <c r="G2" i="1"/>
-  <c r="F2" i="1"/>
-  <c r="E2" i="1"/>
-  <c r="D2" i="1"/>
-  <c r="I2" i="1" s="1"/>
-</calcChain>
-</file>
-
-<file path=xl\persons\person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="358">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="444">
   <si>
     <t>Đạt</t>
   </si>
@@ -138,1120 +94,1433 @@
     <t>Job hệ thống; Máy chủ thư điện tử; Hệ thống file; Quản trị viên; Người khai thác</t>
   </si>
   <si>
-    <t>1. Job định thời kích hoạt quét theo chu kỳ (mặc định 5 phút/lần).
-2. Kết nối hộp thư IMAP/POP3/Exchange và quét thư mục /data/incoming/.
-3. Lấy email chưa đọc/file mới, tải file đính kèm về thư mục tạm.
-4. Kiểm tra phần mở rộng, UTF-8, cấu trúc và kích thước; phân tích theo file mẫu/bảng ánh xạ.
-5. Kiểm tra ràng buộc nghiệp vụ, cập nhật Oracle, lưu bản gốc và ghi audit log.
-6. Di chuyển file theo kết quả xử lý và gửi cảnh báo khi có lỗi.</t>
-  </si>
-  <si>
-    <t>File dữ liệu hợp lệ được chuẩn hóa và cập nhật Oracle trong giao dịch toàn vẹn; bản gốc lưu tại /processed/; audit log đầy đủ; lỗi định dạng vào /error/; vi phạm nghiệp vụ vào /quarantine/ kèm cảnh báo.</t>
-  </si>
-  <si>
-    <t>Quét email và thư mục incoming</t>
-  </si>
-  <si>
-    <t>Kích hoạt job; kết nối máy chủ thư điện tử; đọc email chưa đọc và phát hiện file mới trong /data/incoming/.</t>
-  </si>
-  <si>
-    <t>Hệ thống nhận diện đúng file mới, thông tin tiêu đề/người gửi/thời gian và file đính kèm; không xử lý trùng lặp.</t>
-  </si>
-  <si>
-    <t>Kiểm tra định dạng và phân tích cú pháp</t>
-  </si>
-  <si>
-    <t>Nạp file CSV/XLSX/XML/JSON; kiểm tra phần mở rộng, mã UTF-8, cấu trúc, kích thước; đối chiếu file mẫu và bảng ánh xạ; kiểm tra ràng buộc nghiệp vụ.</t>
-  </si>
-  <si>
-    <t>File hợp lệ được chuẩn hóa; file sai định dạng chuyển /error/ kèm .log WARNING; file vi phạm ràng buộc bị hủy giao dịch và chuyển /quarantine/.</t>
-  </si>
-  <si>
-    <t>Cập nhật cơ sở dữ liệu và lưu trữ bản gốc</t>
-  </si>
-  <si>
-    <t>Ghi dữ liệu đã chuẩn hóa vào Oracle; lưu file gốc; ghi nhật ký kiểm toán; đánh dấu email đã đọc.</t>
-  </si>
-  <si>
-    <t>Dữ liệu cập nhật thành công với toàn vẹn giao dịch; file có tên chuẩn tại /processed/; audit log lưu tối thiểu 5 năm; gửi thông báo hoàn thành.</t>
-  </si>
-  <si>
-    <t>Xử lý ngoại lệ và cảnh báo</t>
-  </si>
-  <si>
-    <t>Mô phỏng file trùng, mất kết nối Oracle, máy chủ email không khả dụng và email không có file đính kèm.</t>
-  </si>
-  <si>
-    <t>File trùng được bỏ qua và ghi log; lỗi DB thử lại tối đa 3 lần rồi cảnh báo CRITICAL; lỗi máy chủ email bỏ qua chu kỳ và cảnh báo sau 3 lần; email không đính kèm được ghi log.</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Thu thập và xử lý dữ liệu ADS-B cho khai thác O/F</t>
-  </si>
-  <si>
-    <t>Cổng ADS-B; Người khai thác ATFM; Job hệ thống; Quản trị viên</t>
-  </si>
-  <si>
-    <t>1. Kết nối cổng ADS-B Gateway và nhận bản tin vị trí theo thời gian thực.
-2. Phân tích, chuẩn hóa và lọc nhiễu bản tin.
-3. Đối chiếu với FPL theo khóa tổng hợp; xác định trạng thái ENTRY/IN-FIR/EXIT trong FIR Hà Nội và Hồ Chí Minh.
-4. Cập nhật trạng thái O/F, lưu trajectory, hiển thị bản đồ/bảng điều khiển và ghi log sự kiện.</t>
-  </si>
-  <si>
-    <t>Dữ liệu O/F cập nhật thời gian thực với độ trễ ≤ 3 giây; trajectory được lưu; chuyến bay không đối chiếu được gắn UNKNOWN_FLIGHT và cảnh báo NOPERM; ghi đủ ENTRY/EXIT.</t>
-  </si>
-  <si>
-    <t>Tiếp nhận và phân tích bản tin ADS-B</t>
-  </si>
-  <si>
-    <t>Kết nối Gateway; nhận bản tin mỗi 1-2 giây; kiểm tra cấu trúc, chuẩn hóa dữ liệu và lọc bản tin nhiễu.</t>
-  </si>
-  <si>
-    <t>Bản tin hợp lệ được xử lý liên tục; dữ liệu sai/ngoài FIR bị loại và ghi log; không làm gián đoạn luồng.</t>
-  </si>
-  <si>
-    <t>Đối chiếu ADS-B với kế hoạch bay FPL</t>
-  </si>
-  <si>
-    <t>Dùng khóa callsign + dep_icao + arr_icao + flight_date để đối chiếu bản tin với FPL.</t>
-  </si>
-  <si>
-    <t>Đối chiếu một-một đúng bản tin/FPL; chuyến bay không khớp được gắn UNKNOWN_FLIGHT và phát cảnh báo NOPERM.</t>
-  </si>
-  <si>
-    <t>Cập nhật trạng thái O/F và trajectory</t>
-  </si>
-  <si>
-    <t>Xác định ENTRY/IN-FIR/EXIT; cập nhật trạng thái theo thời gian thực; lưu đường bay vào flight_trajectory; hiển thị bản đồ và dashboard.</t>
-  </si>
-  <si>
-    <t>Trạng thái cập nhật đúng, độ trễ ≤ 3 giây; trajectory lưu tối thiểu 2 năm; log đầy đủ sự kiện ENTRY/EXIT.</t>
-  </si>
-  <si>
-    <t>Xử lý mất kết nối, mất tín hiệu và xung đột</t>
-  </si>
-  <si>
-    <t>Mô phỏng mất Gateway, gián đoạn đường bay &gt;30 giây, trùng callsign và dữ liệu ngoài FIR Việt Nam.</t>
-  </si>
-  <si>
-    <t>Tự động nối lại có backoff và banner; gắn TRACK_LOST/giữ vị trí cuối; ưu tiên FPL nộp gần nhất; dữ liệu ngoài FIR bị loại và ghi thống kê.</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
-    <t>Kết nối trực tiếp AMHS để gửi/nhận điện văn</t>
-  </si>
-  <si>
-    <t>Cổng AMHS; Quản trị viên; Người khai thác</t>
-  </si>
-  <si>
-    <t>1. Kết nối trực tiếp cơ sở dữ liệu AMHS qua Gateway.
-2. Luồng inbound truy vấn điện văn mới, phân tích AFTN theo ICAO và cập nhật trạng thái chuyến bay.
-3. Luồng outbound chọn chuyến bay/loại điện văn, sinh theo mẫu ICAO, kiểm tra cú pháp và đẩy sang AMHS.
-4. Ghi audit log, xác nhận gửi và xử lý lỗi/quarantine.</t>
-  </si>
-  <si>
-    <t>Điện văn đến cập nhật trạng thái ≤ 5 giây; điện văn đi đúng chuẩn ICAO và có xác nhận; toàn bộ điện văn/audit log được lưu; lỗi vào /quarantine/ và cảnh báo.</t>
-  </si>
-  <si>
-    <t>Nhận và phân tích điện văn AMHS (inbound)</t>
-  </si>
-  <si>
-    <t>Job truy vấn AMHS mỗi 1-5 giây; lấy lô điện văn FPL/DEP/ARR/CHG/CNL/DLA; phân tích cú pháp ICAO và trích xuất dữ liệu.</t>
-  </si>
-  <si>
-    <t>Điện văn hợp lệ được xác thực, cập nhật trạng thái chuyến bay trong ≤ 5 giây; message_id, loại, callsign, hướng, thời gian được ghi log.</t>
-  </si>
-  <si>
-    <t>Sinh và gửi điện văn AMHS (outbound)</t>
-  </si>
-  <si>
-    <t>Người khai thác chọn chuyến bay và loại điện văn; hệ thống tự điền dữ liệu theo template ICAO, kiểm tra cú pháp rồi ghi vào AMHS.</t>
-  </si>
-  <si>
-    <t>Điện văn đúng Doc 4444/4445, gửi thành công kèm xác nhận; trạng thái và audit log được cập nhật.</t>
-  </si>
-  <si>
-    <t>Bảo mật, lưu trữ và kiểm soát tải</t>
-  </si>
-  <si>
-    <t>Kiểm tra TLS 1.3/X.509, mã hóa AES-256 khi lưu, quyền ADMIN_AMHS_CONFIG và tải 5.000 bản tin/giờ (đỉnh 10.000).</t>
-  </si>
-  <si>
-    <t>Kết nối bảo mật, người không đủ quyền bị từ chối; dữ liệu lưu tối thiểu 60 ngày; hệ thống đáp ứng thông lượng yêu cầu.</t>
-  </si>
-  <si>
-    <t>Xử lý mất kết nối, sai cú pháp và trùng điện văn</t>
-  </si>
-  <si>
-    <t>Mô phỏng mất AMHS, điện văn sai ICAO, chứng chỉ hết hạn, điện văn trùng và AMHS quá tải.</t>
-  </si>
-  <si>
-    <t>Xếp hàng và tự kết nối lại; sai cú pháp chuyển /quarantine/ và cảnh báo; cảnh báo chứng chỉ trước 30 ngày; trùng trong 24 giờ bỏ qua; giới hạn tốc độ theo hàng đợi ưu tiên.</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>Tích hợp lọc SLOT vào hệ thống SLB</t>
-  </si>
-  <si>
-    <t>Hệ thống SLOT Cục Hàng không; Nhân viên kế hoạch; Người khai thác ATFM; Quản trị viên</t>
-  </si>
-  <si>
-    <t>1. Đồng bộ dữ liệu SLOT từ Cục Hàng không định kỳ 15 phút.
-2. Nhập KHBN và kích hoạt kiểm tra.
-3. Đối chiếu SLOT với KHBN hãng và KHBN theo phép bay.
-4. Phát hiện trùng, không khả dụng, lệch giờ, chuyến bay không thực hiện.
-5. Cập nhật trạng thái, cảnh báo xung đột và đề xuất điều chỉnh.</t>
-  </si>
-  <si>
-    <t>Mỗi chuyến bay có trạng thái SLOT chính xác (MATCHED/SLOT_MISSING/TIME_CONFLICT/NOT_OPERATED); cảnh báo xung đột trên dashboard/email và đề xuất điều chỉnh.</t>
-  </si>
-  <si>
-    <t>Đồng bộ dữ liệu SLOT định kỳ</t>
-  </si>
-  <si>
-    <t>Chạy bộ định thời hoặc mở màn hình kiểm tra; gọi API/file Cục Hàng không mỗi 15 phút; xác thực dữ liệu.</t>
-  </si>
-  <si>
-    <t>Dữ liệu SLOT được đồng bộ đầy đủ, đúng chu kỳ, không trùng và có nhật ký đồng bộ.</t>
-  </si>
-  <si>
-    <t>Đối chiếu ba nguồn kế hoạch</t>
-  </si>
-  <si>
-    <t>Nạp SLOT đã cấp, KHBN hãng và KHBN theo phép bay; ghép theo chuyến bay, ngày và mã liên quan.</t>
-  </si>
-  <si>
-    <t>Kết quả đối chiếu xác định đúng SLOT hợp lệ/thiếu và chênh lệch giữa ba nguồn.</t>
-  </si>
-  <si>
-    <t>Phân loại xung đột và trạng thái SLOT</t>
-  </si>
-  <si>
-    <t>Tạo dữ liệu trùng SLOT, SLOT không khả dụng, lệch giờ và chuyến bay không thực hiện.</t>
-  </si>
-  <si>
-    <t>Hệ thống gắn đúng MATCHED, SLOT_MISSING, TIME_CONFLICT hoặc NOT_OPERATED; không ghi đè dữ liệu nguồn.</t>
-  </si>
-  <si>
-    <t>Cảnh báo và đề xuất điều chỉnh</t>
-  </si>
-  <si>
-    <t>Kiểm tra màn hình/dashboard và email khi phát hiện xung đột; thử thao tác đề xuất điều chỉnh.</t>
-  </si>
-  <si>
-    <t>Cảnh báo hiển thị đúng đối tượng, đầy đủ chi tiết; đề xuất điều chỉnh giúp điều phối viên xử lý và ghi audit log.</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>Chuẩn hóa API chia sẻ dữ liệu</t>
-  </si>
-  <si>
-    <t>Hệ thống bên ngoài; Quản trị viên; Nhóm phát triển đối tác</t>
-  </si>
-  <si>
-    <t>1. Đăng ký client và cấp thông tin xác thực.
-2. Gọi API REST qua HTTPS theo tài liệu OpenAPI 3.0 bằng OAuth2/JWT/API Key.
-3. Truy vấn dữ liệu chuyến bay, kế hoạch bay, thống kê với tham số JSON.
-4. Kiểm tra phân quyền phạm vi, giới hạn tốc độ và định dạng phản hồi.
-5. Ghi audit log toàn bộ truy cập và xử lý lỗi.</t>
-  </si>
-  <si>
-    <t>API thống nhất, phản hồi đúng schema OpenAPI 3.0; xác thực/phân quyền hoạt động; giới hạn tốc độ theo client; mọi truy cập được audit.</t>
-  </si>
-  <si>
-    <t>Xác thực và cấp quyền API</t>
-  </si>
-  <si>
-    <t>Gửi request HTTPS với Bearer JWT/API Key hợp lệ, hết hạn, sai chữ ký và scope không đủ.</t>
-  </si>
-  <si>
-    <t>Token hợp lệ được truy cập đúng phạm vi; token sai/hết hạn hoặc thiếu scope trả lỗi 401/403, không lộ dữ liệu.</t>
-  </si>
-  <si>
-    <t>Truy vấn và chuẩn hóa phản hồi</t>
-  </si>
-  <si>
-    <t>Gọi endpoint dữ liệu chuyến bay/kế hoạch/thống kê với tham số JSON hợp lệ, thiếu và sai kiểu.</t>
-  </si>
-  <si>
-    <t>Phản hồi JSON đúng schema, mã HTTP và thông báo lỗi nhất quán; tham số không hợp lệ bị từ chối an toàn.</t>
-  </si>
-  <si>
-    <t>Giới hạn tốc độ và kiểm soát tải</t>
-  </si>
-  <si>
-    <t>Gửi số request vượt ngưỡng của một client trong khoảng thời gian cấu hình.</t>
-  </si>
-  <si>
-    <t>API áp dụng rate limit theo client, trả HTTP 429 khi vượt ngưỡng và không ảnh hưởng client khác.</t>
-  </si>
-  <si>
-    <t>Audit log và xử lý sự cố API</t>
-  </si>
-  <si>
-    <t>Kiểm tra log với request thành công/thất bại; mô phỏng API lỗi, timeout và truy vấn không có dữ liệu.</t>
-  </si>
-  <si>
-    <t>Audit log ghi user/client, endpoint, thời gian, kết quả; lỗi trả thông báo chuẩn, không có dữ liệu trả rỗng; không rò rỉ thông tin nhạy cảm.</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
-    <t>Hệ thống cảnh báo thông minh đa kịch bản</t>
-  </si>
-  <si>
-    <t>Công cụ quy tắc; Quản trị viên; Người khai thác</t>
-  </si>
-  <si>
-    <t>1. Cấu hình bộ quy tắc và kênh thông báo.
-2. Phát sinh sự kiện bất thường.
-3. Bộ xử lý sự kiện phức hợp đánh giá điều kiện và mức độ.
-4. Gửi cảnh báo đa kênh, cập nhật trạng thái xử lý và ghi log.</t>
-  </si>
-  <si>
-    <t>Cảnh báo đúng kịch bản/mức độ, gửi đúng kênh, chống lặp; trạng thái được cập nhật và truy vết đầy đủ.</t>
-  </si>
-  <si>
-    <t>Cấu hình quy tắc và kênh cảnh báo</t>
-  </si>
-  <si>
-    <t>Quản trị viên tạo/bật/tắt quy tắc, đặt ngưỡng, mức độ và kênh dashboard/email/SMS.</t>
-  </si>
-  <si>
-    <t>Quy tắc lưu đúng phiên bản; chỉ người có quyền được cấu hình; kênh gửi hoạt động theo cấu hình.</t>
-  </si>
-  <si>
-    <t>Phát hiện và đánh giá sự kiện</t>
-  </si>
-  <si>
-    <t>Phát sinh các sự kiện vượt ngưỡng, chuỗi sự kiện và sự kiện trùng trong thời gian ngắn.</t>
-  </si>
-  <si>
-    <t>Hệ thống phát hiện theo thời gian thực, gộp sự kiện đúng điều kiện, xác định đúng mức cảnh báo và không gửi lặp ngoài chính sách.</t>
-  </si>
-  <si>
-    <t>Gửi, tiếp nhận và xử lý cảnh báo</t>
-  </si>
-  <si>
-    <t>Kiểm tra cảnh báo trên dashboard/email/SMS; người khai thác xác nhận, phân công và đóng cảnh báo.</t>
-  </si>
-  <si>
-    <t>Cảnh báo đến đúng người/nhóm; trạng thái New-Acknowledged-In progress-Resolved được ghi nhận; toàn bộ thao tác có audit log.</t>
-  </si>
-  <si>
-    <t>Xử lý lỗi và chống bão cảnh báo</t>
-  </si>
-  <si>
-    <t>Mô phỏng kênh thông báo lỗi, dịch vụ không khả dụng và số lượng cảnh báo tăng đột biến.</t>
-  </si>
-  <si>
-    <t>Có retry/fallback, lưu hàng đợi khi cần; cảnh báo được gom/giới hạn tần suất; quản trị viên nhận thông báo lỗi.</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
-    <t>Quản lý thông tin KHB quân sự và sử dụng vùng trời</t>
-  </si>
-  <si>
-    <t>Người khai thác ATFM/QLB; Quản trị viên; Cấp phê duyệt</t>
-  </si>
-  <si>
-    <t>1. Nhập KHB quân sự và thông tin vùng trời.
-2. Kiểm tra quyền, phê duyệt và đồng bộ dữ liệu.
-3. Đối chiếu với chuyến bay dân sự để phát hiện xung đột vùng trời.
-4. Cảnh báo, ghi nhận xử lý và bảo vệ dữ liệu nhạy cảm.</t>
-  </si>
-  <si>
-    <t>KHB quân sự được nhập/phê duyệt đúng quyền, đồng bộ an toàn; xung đột vùng trời được phát hiện/cảnh báo; dữ liệu được bảo mật và audit.</t>
-  </si>
-  <si>
-    <t>Nhập và phê duyệt KHB quân sự</t>
-  </si>
-  <si>
-    <t>Người khai thác nhập KHB; cấp phê duyệt xem xét và phê duyệt/từ chối theo quy trình.</t>
-  </si>
-  <si>
-    <t>Dữ liệu hợp lệ được lưu; người không đủ quyền bị từ chối; lịch sử phê duyệt và lý do được ghi log.</t>
-  </si>
-  <si>
-    <t>Cấu hình vùng trời và phân quyền</t>
-  </si>
-  <si>
-    <t>Quản trị viên cấu hình vùng trời dùng chung, clearance level và vai trò truy cập.</t>
-  </si>
-  <si>
-    <t>Chỉ tài khoản đúng clearance truy cập dữ liệu; thay đổi cấu hình có hiệu lực đúng phạm vi và audit.</t>
-  </si>
-  <si>
-    <t>Đồng bộ và đối chiếu quân-dân sự</t>
-  </si>
-  <si>
-    <t>Đồng bộ KHB quân sự với dữ liệu chuyến bay dân sự; tạo lịch bay giao cắt vùng trời/thời gian.</t>
-  </si>
-  <si>
-    <t>Hệ thống phát hiện đúng xung đột, hiển thị chi tiết trên dashboard và không làm lộ dữ liệu ngoài phạm vi.</t>
-  </si>
-  <si>
-    <t>Cảnh báo và xử lý xung đột vùng trời</t>
-  </si>
-  <si>
-    <t>Mô phỏng xung đột, KHB bị hủy/sửa và truy cập trái phép dữ liệu quân sự.</t>
-  </si>
-  <si>
-    <t>Cảnh báo gửi đúng đối tượng; dữ liệu được cập nhật/thu hồi nhất quán; truy cập trái phép bị chặn và ghi sự kiện bảo mật.</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>MỞ RỘNG THỜI GIAN LƯU TRỮ ĐIỆN VĂN INBOX</t>
-  </si>
-  <si>
-    <t>Người khai thác ATFM/QLB; Quản trị viên</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: MỞ RỘNG THỜI GIAN LƯU TRỮ ĐIỆN VĂN INBOX</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: MỞ RỘNG THỜI GIAN LƯU TRỮ ĐIỆN VĂN INBOX.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng MỞ RỘNG THỜI GIAN LƯU TRỮ ĐIỆN VĂN INBOX; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>CẢNH BÁO NOPERM CHO ĐIỆN VĂN KHÔNG CÓ TRONG KHBN</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: CẢNH BÁO NOPERM CHO ĐIỆN VĂN KHÔNG CÓ TRONG KHBN</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: CẢNH BÁO NOPERM CHO ĐIỆN VĂN KHÔNG CÓ TRONG KHBN.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng CẢNH BÁO NOPERM CHO ĐIỆN VĂN KHÔNG CÓ TRONG KHBN; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>3.3</t>
-  </si>
-  <si>
-    <t>ÁP DỤNG QUY TẮC 120H ICAO CHO HIỂN THỊ FPL</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: ÁP DỤNG QUY TẮC 120H ICAO CHO HIỂN THỊ FPL</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: ÁP DỤNG QUY TẮC 120H ICAO CHO HIỂN THỊ FPL.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng ÁP DỤNG QUY TẮC 120H ICAO CHO HIỂN THỊ FPL; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
-    <t>TÌM KIẾM CHUYẾN BAY ĐA TRƯỜNG, HỖ TRỢ TÌM KIẾM THEO TỪ KHÓA</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TÌM KIẾM CHUYẾN BAY ĐA TRƯỜNG, HỖ TRỢ TÌM KIẾM THEO TỪ KHÓA</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: TÌM KIẾM CHUYẾN BAY ĐA TRƯỜNG, HỖ TRỢ TÌM KIẾM THEO TỪ KHÓA.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng TÌM KIẾM CHUYẾN BAY ĐA TRƯỜNG, HỖ TRỢ TÌM KIẾM THEO TỪ KHÓA; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>TÌM KIẾM NÂNG CAO PHỤC VỤ BÁO CÁO</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TÌM KIẾM NÂNG CAO PHỤC VỤ BÁO CÁO</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: TÌM KIẾM NÂNG CAO PHỤC VỤ BÁO CÁO.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng TÌM KIẾM NÂNG CAO PHỤC VỤ BÁO CÁO; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>3.6</t>
-  </si>
-  <si>
-    <t>PHÂN LOẠI CHUYẾN BAY QUỐC NỘI/QUỐC TẾ TỰ ĐỘNG</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: PHÂN LOẠI CHUYẾN BAY QUỐC NỘI/QUỐC TẾ TỰ ĐỘNG</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: PHÂN LOẠI CHUYẾN BAY QUỐC NỘI/QUỐC TẾ TỰ ĐỘNG.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng PHÂN LOẠI CHUYẾN BAY QUỐC NỘI/QUỐC TẾ TỰ ĐỘNG; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>3.7</t>
-  </si>
-  <si>
-    <t>EXPORT DỮ LIỆU CHIA TÁCH 3 LOẠI FILE (ALL, LD, OF)</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: EXPORT DỮ LIỆU CHIA TÁCH 3 LOẠI FILE (ALL, LD, OF)</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: EXPORT DỮ LIỆU CHIA TÁCH 3 LOẠI FILE (ALL, LD, OF).
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng EXPORT DỮ LIỆU CHIA TÁCH 3 LOẠI FILE (ALL, LD, OF); dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t>CHỈNH SỬA THÔNG TIN CHUYẾN BAY</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: CHỈNH SỬA THÔNG TIN CHUYẾN BAY</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: CHỈNH SỬA THÔNG TIN CHUYẾN BAY.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng CHỈNH SỬA THÔNG TIN CHUYẾN BAY; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>HIỂN THỊ LỊCH SỬ THAO TÁC CỦA NGƯỜI XỬ LÝ CHUYẾN BAY</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: HIỂN THỊ LỊCH SỬ THAO TÁC CỦA NGƯỜI XỬ LÝ CHUYẾN BAY</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: HIỂN THỊ LỊCH SỬ THAO TÁC CỦA NGƯỜI XỬ LÝ CHUYẾN BAY.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng HIỂN THỊ LỊCH SỬ THAO TÁC CỦA NGƯỜI XỬ LÝ CHUYẾN BAY; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>ĐỒNG BỘ DỮ LIỆU ĐIỆN VĂN LIÊN NGÀY (DEP CUỐI NGÀY → ARR HÔM SAU)</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: ĐỒNG BỘ DỮ LIỆU ĐIỆN VĂN LIÊN NGÀY (DEP CUỐI NGÀY → ARR HÔM SAU)</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: ĐỒNG BỘ DỮ LIỆU ĐIỆN VĂN LIÊN NGÀY (DEP CUỐI NGÀY → ARR HÔM SAU).
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng ĐỒNG BỘ DỮ LIỆU ĐIỆN VĂN LIÊN NGÀY (DEP CUỐI NGÀY → ARR HÔM SAU); dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>THỐNG KÊ THEO KHUNG GIỜ/CHẶNG/ĐƯỜNG BAY</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: THỐNG KÊ THEO KHUNG GIỜ/CHẶNG/ĐƯỜNG BAY</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: THỐNG KÊ THEO KHUNG GIỜ/CHẶNG/ĐƯỜNG BAY.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng THỐNG KÊ THEO KHUNG GIỜ/CHẶNG/ĐƯỜNG BAY; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>CẢNH BÁO CHUYẾN BAY KHÔNG CÓ TRONG PHÉP BAY/KHB NGÀY</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: CẢNH BÁO CHUYẾN BAY KHÔNG CÓ TRONG PHÉP BAY/KHB NGÀY</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: CẢNH BÁO CHUYẾN BAY KHÔNG CÓ TRONG PHÉP BAY/KHB NGÀY.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng CẢNH BÁO CHUYẾN BAY KHÔNG CÓ TRONG PHÉP BAY/KHB NGÀY; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.3</t>
-  </si>
-  <si>
-    <t>HỖ TRỢ HỦY PHÉP BAY QUỐC TẾ/QUỐC NỘI</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: HỖ TRỢ HỦY PHÉP BAY QUỐC TẾ/QUỐC NỘI</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: HỖ TRỢ HỦY PHÉP BAY QUỐC TẾ/QUỐC NỘI.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng HỖ TRỢ HỦY PHÉP BAY QUỐC TẾ/QUỐC NỘI; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.4</t>
-  </si>
-  <si>
-    <t>TỐI ƯU HIỆU NĂNG EXPORT BRAVO (&lt; 3 PHÚT)</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TỐI ƯU HIỆU NĂNG EXPORT BRAVO (&lt; 3 PHÚT)</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: TỐI ƯU HIỆU NĂNG EXPORT BRAVO (&lt; 3 PHÚT).
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng TỐI ƯU HIỆU NĂNG EXPORT BRAVO (&lt; 3 PHÚT); dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.5</t>
-  </si>
-  <si>
-    <t>CHỨC NĂNG F8 "ÉP DÒNG" TRONG CALENDAR ACCEPTED</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: CHỨC NĂNG F8 "ÉP DÒNG" TRONG CALENDAR ACCEPTED</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: CHỨC NĂNG F8 "ÉP DÒNG" TRONG CALENDAR ACCEPTED.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng CHỨC NĂNG F8 "ÉP DÒNG" TRONG CALENDAR ACCEPTED; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>TỐI ƯU GEN KHB NGÀY HÔM SAU RA AFTN (&lt; 3 PHÚT)</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TỐI ƯU GEN KHB NGÀY HÔM SAU RA AFTN (&lt; 3 PHÚT)</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: TỐI ƯU GEN KHB NGÀY HÔM SAU RA AFTN (&lt; 3 PHÚT).
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng TỐI ƯU GEN KHB NGÀY HÔM SAU RA AFTN (&lt; 3 PHÚT); dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>MỞ RỘNG PHẠM VI TRA CỨU INBOX (&gt; 7 NGÀY)</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: MỞ RỘNG PHẠM VI TRA CỨU INBOX (&gt; 7 NGÀY)</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: MỞ RỘNG PHẠM VI TRA CỨU INBOX (&gt; 7 NGÀY).
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng MỞ RỘNG PHẠM VI TRA CỨU INBOX (&gt; 7 NGÀY); dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>TỰ ĐỘNG CẬP NHẬT KHI SỬA KHB ĐÃ BUILD</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TỰ ĐỘNG CẬP NHẬT KHI SỬA KHB ĐÃ BUILD</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: TỰ ĐỘNG CẬP NHẬT KHI SỬA KHB ĐÃ BUILD.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng TỰ ĐỘNG CẬP NHẬT KHI SỬA KHB ĐÃ BUILD; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>CẢNH BÁO CHUYẾN BAY CẤP SAI NGÀY BAY SO VỚI NGÀY BAY THỰC TẾ</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: CẢNH BÁO CHUYẾN BAY CẤP SAI NGÀY BAY SO VỚI NGÀY BAY THỰC TẾ</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: CẢNH BÁO CHUYẾN BAY CẤP SAI NGÀY BAY SO VỚI NGÀY BAY THỰC TẾ.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng CẢNH BÁO CHUYẾN BAY CẤP SAI NGÀY BAY SO VỚI NGÀY BAY THỰC TẾ; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>BỔ SUNG TRƯỜNG "MỤC ĐÍCH CHUYẾN BAY" TRONG KHB NGÀY</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: BỔ SUNG TRƯỜNG "MỤC ĐÍCH CHUYẾN BAY" TRONG KHB NGÀY</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: BỔ SUNG TRƯỜNG "MỤC ĐÍCH CHUYẾN BAY" TRONG KHB NGÀY.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng BỔ SUNG TRƯỜNG "MỤC ĐÍCH CHUYẾN BAY" TRONG KHB NGÀY; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>LOGIC CẢNH BÁO "ĐỎ" CHÍNH XÁC CHO CHUYẾN BAY HẾT HIỆU LỰC</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: LOGIC CẢNH BÁO "ĐỎ" CHÍNH XÁC CHO CHUYẾN BAY HẾT HIỆU LỰC</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: LOGIC CẢNH BÁO "ĐỎ" CHÍNH XÁC CHO CHUYẾN BAY HẾT HIỆU LỰC.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng LOGIC CẢNH BÁO "ĐỎ" CHÍNH XÁC CHO CHUYẾN BAY HẾT HIỆU LỰC; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>TỰ ĐỘNG CẬP NHẬT ĐƯỜNG BAY THEO ĐOẠN TỪ FPL THỰC TẾ</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TỰ ĐỘNG CẬP NHẬT ĐƯỜNG BAY THEO ĐOẠN TỪ FPL THỰC TẾ</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: TỰ ĐỘNG CẬP NHẬT ĐƯỜNG BAY THEO ĐOẠN TỪ FPL THỰC TẾ.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng TỰ ĐỘNG CẬP NHẬT ĐƯỜNG BAY THEO ĐOẠN TỪ FPL THỰC TẾ; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>TỰ ĐỘNG NHẬN DIỆN VÀ CHUYỂN NGÀY CHO CHUYẾN BAY QUỐC TẾ HẠ CÁNH HÔM SAU</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TỰ ĐỘNG NHẬN DIỆN VÀ CHUYỂN NGÀY CHO CHUYẾN BAY QUỐC TẾ HẠ CÁNH HÔM SAU</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: TỰ ĐỘNG NHẬN DIỆN VÀ CHUYỂN NGÀY CHO CHUYẾN BAY QUỐC TẾ HẠ CÁNH HÔM SAU.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng TỰ ĐỘNG NHẬN DIỆN VÀ CHUYỂN NGÀY CHO CHUYẾN BAY QUỐC TẾ HẠ CÁNH HÔM SAU; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.4</t>
-  </si>
-  <si>
-    <t>THEO DÕI KẾ HOẠCH BAY HÀNG NGÀY VỚI CẬP NHẬT LIÊN TỤC</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: THEO DÕI KẾ HOẠCH BAY HÀNG NGÀY VỚI CẬP NHẬT LIÊN TỤC</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: THEO DÕI KẾ HOẠCH BAY HÀNG NGÀY VỚI CẬP NHẬT LIÊN TỤC.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng THEO DÕI KẾ HOẠCH BAY HÀNG NGÀY VỚI CẬP NHẬT LIÊN TỤC; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>THÔNG BÁO THỜI ĐIỂM NHẬN SỐ LIỆU BAY ĐI/ĐẾN TỪ TRUNG TÂM TBHĐB</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: THÔNG BÁO THỜI ĐIỂM NHẬN SỐ LIỆU BAY ĐI/ĐẾN TỪ TRUNG TÂM TBHĐB</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: THÔNG BÁO THỜI ĐIỂM NHẬN SỐ LIỆU BAY ĐI/ĐẾN TỪ TRUNG TÂM TBHĐB.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng THÔNG BÁO THỜI ĐIỂM NHẬN SỐ LIỆU BAY ĐI/ĐẾN TỪ TRUNG TÂM TBHĐB; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>CẬP NHẬT SỐ LIỆU BAY TỪ SLB SANG BRAVO</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: CẬP NHẬT SỐ LIỆU BAY TỪ SLB SANG BRAVO</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: CẬP NHẬT SỐ LIỆU BAY TỪ SLB SANG BRAVO.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng CẬP NHẬT SỐ LIỆU BAY TỪ SLB SANG BRAVO; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.7</t>
-  </si>
-  <si>
-    <t>KHẮC PHỤC LỖI NHẦM NGÀY SO VỚI THỰC TẾ</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: KHẮC PHỤC LỖI NHẦM NGÀY SO VỚI THỰC TẾ</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: KHẮC PHỤC LỖI NHẦM NGÀY SO VỚI THỰC TẾ.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng KHẮC PHỤC LỖI NHẦM NGÀY SO VỚI THỰC TẾ; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.8</t>
-  </si>
-  <si>
-    <t>SỬA NHIỀU CHUYẾN BAY CÙNG NỘI DUNG TRONG MỘT THAO TÁC</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: SỬA NHIỀU CHUYẾN BAY CÙNG NỘI DUNG TRONG MỘT THAO TÁC</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: SỬA NHIỀU CHUYẾN BAY CÙNG NỘI DUNG TRONG MỘT THAO TÁC.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng SỬA NHIỀU CHUYẾN BAY CÙNG NỘI DUNG TRONG MỘT THAO TÁC; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>ĐỐI CHIẾU SỐ LIỆU BAY GIỮA SLB VÀ BRAVO</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: ĐỐI CHIẾU SỐ LIỆU BAY GIỮA SLB VÀ BRAVO</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: ĐỐI CHIẾU SỐ LIỆU BAY GIỮA SLB VÀ BRAVO.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng ĐỐI CHIẾU SỐ LIỆU BAY GIỮA SLB VÀ BRAVO; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>MỞ RỘNG TÌM KIẾM TRÊN GIAO DIỆN DAILY MILITARY REPORT</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: MỞ RỘNG TÌM KIẾM TRÊN GIAO DIỆN DAILY MILITARY REPORT</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: MỞ RỘNG TÌM KIẾM TRÊN GIAO DIỆN DAILY MILITARY REPORT.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng MỞ RỘNG TÌM KIẾM TRÊN GIAO DIỆN DAILY MILITARY REPORT; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>THÊM LỰA CHỌN THEO TẤT CẢ TIÊU CHÍ THỐNG KÊ TRONG BÁO CÁO</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: THÊM LỰA CHỌN THEO TẤT CẢ TIÊU CHÍ THỐNG KÊ TRONG BÁO CÁO</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: THÊM LỰA CHỌN THEO TẤT CẢ TIÊU CHÍ THỐNG KÊ TRONG BÁO CÁO.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng THÊM LỰA CHỌN THEO TẤT CẢ TIÊU CHÍ THỐNG KÊ TRONG BÁO CÁO; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>ĐÁNH GIÁ SO SÁNH SỐ LIỆU CỦA KHBHĐBN VỚI CÙNG KỲ TUẦN TRƯỚC</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: ĐÁNH GIÁ SO SÁNH SỐ LIỆU CỦA KHBHĐBN VỚI CÙNG KỲ TUẦN TRƯỚC</t>
-  </si>
-  <si>
-    <t>1. Mở chức năng và chuẩn bị dữ liệu kiểm thử liên quan đến: ĐÁNH GIÁ SO SÁNH SỐ LIỆU CỦA KHBHĐBN VỚI CÙNG KỲ TUẦN TRƯỚC.
-2. Thực hiện thao tác theo yêu cầu nghiệp vụ, gồm cả trường hợp hợp lệ và ngoại lệ.
-3. Kiểm tra dữ liệu hiển thị, trạng thái xử lý, thông báo và nhật ký.</t>
-  </si>
-  <si>
-    <t>Hệ thống thực hiện đúng chức năng ĐÁNH GIÁ SO SÁNH SỐ LIỆU CỦA KHBHĐBN VỚI CÙNG KỲ TUẦN TRƯỚC; dữ liệu và trạng thái được cập nhật nhất quán, kết quả hiển thị đúng, lỗi được cảnh báo/xử lý an toàn và thao tác được ghi audit log.</t>
-  </si>
-  <si>
-    <t>BIỂU ĐỒ THÔNG TIN TỔNG QUAN KHAI THÁC BAY</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: BIỂU ĐỒ THÔNG TIN TỔNG QUAN KHAI THÁC BAY</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: BIỂU ĐỒ THÔNG TIN TỔNG QUAN KHAI THÁC BAY.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả BIỂU ĐỒ THÔNG TIN TỔNG QUAN KHAI THÁC BAY chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>PHÂN TÍCH XU HƯỚNG KHAI THÁC THEO THỜI GIAN</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: PHÂN TÍCH XU HƯỚNG KHAI THÁC THEO THỜI GIAN</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: PHÂN TÍCH XU HƯỚNG KHAI THÁC THEO THỜI GIAN.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả PHÂN TÍCH XU HƯỚNG KHAI THÁC THEO THỜI GIAN chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>PHÁT HIỆN VÀ CẢNH BÁO DỮ LIỆU BẤT THƯỜNG</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: PHÁT HIỆN VÀ CẢNH BÁO DỮ LIỆU BẤT THƯỜNG</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: PHÁT HIỆN VÀ CẢNH BÁO DỮ LIỆU BẤT THƯỜNG.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả PHÁT HIỆN VÀ CẢNH BÁO DỮ LIỆU BẤT THƯỜNG chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>TÍCH HỢP ADS-B CHO BÁO CÁO KHAI THÁC THỰC TẾ</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TÍCH HỢP ADS-B CHO BÁO CÁO KHAI THÁC THỰC TẾ</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: TÍCH HỢP ADS-B CHO BÁO CÁO KHAI THÁC THỰC TẾ.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả TÍCH HỢP ADS-B CHO BÁO CÁO KHAI THÁC THỰC TẾ chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>TỔNG HỢP CHỈ SỐ HIỆU SUẤT BAY TỪ ADS-B</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: TỔNG HỢP CHỈ SỐ HIỆU SUẤT BAY TỪ ADS-B</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: TỔNG HỢP CHỈ SỐ HIỆU SUẤT BAY TỪ ADS-B.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả TỔNG HỢP CHỈ SỐ HIỆU SUẤT BAY TỪ ADS-B chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>BIỂU ĐỒ THỐNG KÊ TRẠNG THÁI CHUYẾN BAY THEO TỶ LỆ %</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: BIỂU ĐỒ THỐNG KÊ TRẠNG THÁI CHUYẾN BAY THEO TỶ LỆ %</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: BIỂU ĐỒ THỐNG KÊ TRẠNG THÁI CHUYẾN BAY THEO TỶ LỆ %.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả BIỂU ĐỒ THỐNG KÊ TRẠNG THÁI CHUYẾN BAY THEO TỶ LỆ % chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>BIỂU ĐỒ SO SÁNH HOẠT ĐỘNG BAY GIỮA CÁC SÂN BAY</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: BIỂU ĐỒ SO SÁNH HOẠT ĐỘNG BAY GIỮA CÁC SÂN BAY</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: BIỂU ĐỒ SO SÁNH HOẠT ĐỘNG BAY GIỮA CÁC SÂN BAY.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả BIỂU ĐỒ SO SÁNH HOẠT ĐỘNG BAY GIỮA CÁC SÂN BAY chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>BÁO CÁO CHUYẾN BAY QUÂN SỰ THEO TIÊU CHÍ MỞ RỘNG</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: BÁO CÁO CHUYẾN BAY QUÂN SỰ THEO TIÊU CHÍ MỞ RỘNG</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: BÁO CÁO CHUYẾN BAY QUÂN SỰ THEO TIÊU CHÍ MỞ RỘNG.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả BÁO CÁO CHUYẾN BAY QUÂN SỰ THEO TIÊU CHÍ MỞ RỘNG chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>BÁO CÁO TỔNG HỢP HOẠT ĐỘNG BAY TẤT CẢ SÂN BAY DÂN DỤNG</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: BÁO CÁO TỔNG HỢP HOẠT ĐỘNG BAY TẤT CẢ SÂN BAY DÂN DỤNG</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: BÁO CÁO TỔNG HỢP HOẠT ĐỘNG BAY TẤT CẢ SÂN BAY DÂN DỤNG.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả BÁO CÁO TỔNG HỢP HOẠT ĐỘNG BAY TẤT CẢ SÂN BAY DÂN DỤNG chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>BÁO CÁO CẤT, HẠ CÁNH TẠI CÁC SÂN BAY TOÀN QUỐC</t>
-  </si>
-  <si>
-    <t>Kiểm thử chức năng: BÁO CÁO CẤT, HẠ CÁNH TẠI CÁC SÂN BAY TOÀN QUỐC</t>
-  </si>
-  <si>
-    <t>1. Mở báo cáo/chức năng và chọn khoảng thời gian, phạm vi dữ liệu.
-2. Thực hiện truy vấn, tổng hợp hoặc hiển thị biểu đồ theo yêu cầu: BÁO CÁO CẤT, HẠ CÁNH TẠI CÁC SÂN BAY TOÀN QUỐC.
-3. Kiểm tra bộ lọc, số liệu, drill-down, cảnh báo và chức năng xuất báo cáo.</t>
-  </si>
-  <si>
-    <t>Kết quả BÁO CÁO CẤT, HẠ CÁNH TẠI CÁC SÂN BAY TOÀN QUỐC chính xác, nhất quán với dữ liệu nguồn; biểu đồ/bảng cập nhật đúng bộ lọc, quyền truy cập được áp dụng, lỗi được thông báo và thao tác ghi audit log.</t>
-  </si>
-  <si>
-    <t>XỬ LÝ NGÔN NGỮ TỰ NHIÊN CHO TRUY VẤN HÀNG KHÔNG</t>
-  </si>
-  <si>
-    <t>Người khai thác; NLP Engine; Từ điển hàng không</t>
-  </si>
-  <si>
-    <t>Phân tích câu hỏi tiếng Việt thành truy vấn cấu trúc</t>
-  </si>
-  <si>
-    <t>Nhập câu hỏi tiếng Việt có dấu/không dấu, viết tắt hoặc teencode; hệ thống chuẩn hóa, phân loại intent, nhận diện thực thể và đối chiếu từ điển.</t>
-  </si>
-  <si>
-    <t>Trả về JSON AST đúng intent/entities; hỗ trợ biến thể tiếng Việt; câu hỏi mơ hồ được yêu cầu làm rõ; không sinh truy vấn ngoài phạm vi.</t>
-  </si>
-  <si>
-    <t>TRUY VẤN VÀ TỔNG HỢP DỮ LIỆU TỰ ĐỘNG THEO YÊU CẦU</t>
-  </si>
-  <si>
-    <t>Người khai thác; NLP Engine; Semantic Layer; RBAC</t>
-  </si>
-  <si>
-    <t>Sinh và thực thi truy vấn an toàn từ JSON AST</t>
-  </si>
-  <si>
-    <t>Gửi JSON AST; xác thực qua Semantic Layer; áp dụng RBAC; sinh parameterized SQL; thực thi với timeout guard và định dạng kết quả.</t>
-  </si>
-  <si>
-    <t>Dữ liệu truy xuất chính xác, không SQL injection; quyền được áp dụng trước khi chạm DB; timeout được kiểm soát; trả JSON/Rich Cards hoặc thông báo không có dữ liệu.</t>
-  </si>
-  <si>
-    <t>TÍCH HỢP TRỢ LÝ ẢO (CHATBOT) VÀO GIAO DIỆN SLB</t>
-  </si>
-  <si>
-    <t>Người khai thác; Chatbot backend; WebSocket; Web Speech API</t>
-  </si>
-  <si>
-    <t>Tương tác chatbot đa phương thức và deep-link</t>
-  </si>
-  <si>
-    <t>Mở chatbot bằng Ctrl+K/icon; nhập text hoặc voice-to-text; kiểm tra suggested queries theo ngữ cảnh, streaming response và deep-link đến màn hình nghiệp vụ.</t>
-  </si>
-  <si>
-    <t>Chatbot truy cập từ mọi màn hình; phản hồi streaming đúng ngữ cảnh; voice lỗi có fallback text; mất WebSocket tự reconnect; deep-link mở đúng chức năng.</t>
-  </si>
-  <si>
-    <t>BÁO CÁO VÀ GIÁM SÁT HIỆU NĂNG CỦA TRỢ LÝ ẢO</t>
-  </si>
-  <si>
-    <t>Quản trị viên; AI Ops Dashboard; Telemetry Service</t>
-  </si>
-  <si>
-    <t>Theo dõi metrics, fallback và active learning</t>
-  </si>
-  <si>
-    <t>Ghi telemetry mọi tương tác; xem Volume, Accuracy Rate, Intent Distribution, Top Fallback; review query lỗi, gán lại intent/entity và kích hoạt retrain.</t>
-  </si>
-  <si>
-    <t>Dashboard hiển thị metrics gần thời gian thực; fallback rate vượt ngưỡng phát cảnh báo; PII được che trước khi lưu; retrain không cần restart và có audit log.</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu ra</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 1.
+2. Thực hiện chuỗi nghiệp vụ: System kiểm tra thư mục theo lịch trình → Phát hiện file mới → Validate định dạng → Parse dữ liệu → Cập nhật vào CSDL → Ghi log và thông báo kết quả.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 1, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 2: File lỗi định dạng → Hệ thống chuyển vào thư mục error và gửi cảnh báo cho Admin</t>
+  </si>
+  <si>
+    <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu vào</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 2</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 2.
+2. Thực hiện chuỗi nghiệp vụ: File lỗi định dạng → Hệ thống chuyển vào thư mục error và gửi cảnh báo cho Admin.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 2, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 3: Nhận file dữ liệu ADS-B → Match với kế hoạch bay → Cập nhật trạng thái O/F → Hiển thị real-time trên map/dashboard</t>
+  </si>
+  <si>
+    <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu vào/ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 3</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 3.
+2. Thực hiện chuỗi nghiệp vụ: Nhận file dữ liệu ADS-B → Match với kế hoạch bay → Cập nhật trạng thái O/F → Hiển thị real-time trên map/dashboard.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 3, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 4: Nhập thông tin chuyến bay SLOT → Nhập thông tin kế hoạch ngày của hãng → Kiểm tra trùng/khả dụng → Đưa ra danh sách chuyên bay không diễn ra → Xác nhận và lưu vào kế hoạch</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 4</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 4.
+2. Thực hiện chuỗi nghiệp vụ: Nhập thông tin chuyến bay SLOT → Nhập thông tin kế hoạch ngày của hãng → Kiểm tra trùng/khả dụng → Đưa ra danh sách chuyên bay không diễn ra → Xác nhận và lưu vào kế hoạch.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 4, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 5: Hệ thống truy cập vào cơ sở dữ liệu điện văn của AMHS → Đọc và phân tích điện văn → Cập nhật trạng thái và lưu log</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 5</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 5.
+2. Thực hiện chuỗi nghiệp vụ: Hệ thống truy cập vào cơ sở dữ liệu điện văn của AMHS → Đọc và phân tích điện văn → Cập nhật trạng thái và lưu log.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 5, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 6: Hệ thống xuất dữ liệu điện văn vào bảng cơ sở dữ liệu điện văn của AMHS → Cập nhật trạng thái và lưu log</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 6</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 6.
+2. Thực hiện chuỗi nghiệp vụ: Hệ thống xuất dữ liệu điện văn vào bảng cơ sở dữ liệu điện văn của AMHS → Cập nhật trạng thái và lưu log.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 6, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 7: Client gửi request với token → API Gateway validate → Router đến service tương ứng → Trả về dữ liệu định dạng JSON → Ghi audit log</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 7</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 7.
+2. Thực hiện chuỗi nghiệp vụ: Client gửi request với token → API Gateway validate → Router đến service tương ứng → Trả về dữ liệu định dạng JSON → Ghi audit log.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 7, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 8: Engine giám sát sự kiện thời gian thực → So sánh với rule set → Kích hoạt cảnh báo khi match → Gửi notification → Ghi nhận trạng thái xử lý \n32</t>
+  </si>
+  <si>
+    <t>NHÓM 2: CẢNH BÁO &amp; TIỆN ÍCH HỖ TRỢ; Phân loại: Dữ liệu đầu ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 8</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 8.
+2. Thực hiện chuỗi nghiệp vụ: Engine giám sát sự kiện thời gian thực → So sánh với rule set → Kích hoạt cảnh báo khi match → Gửi notification → Ghi nhận trạng thái xử lý \n32.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 8, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 9: Nhập KHB quân sự → Gửi chờ duyệt → Đề xuất điều chỉnh (nếu cần) → Phê duyệt → Thông báo tự động cho các bên liên quan HTSLB</t>
+  </si>
+  <si>
+    <t>NHÓM 2: CẢNH BÁO &amp; TIỆN ÍCH HỖ TRỢ; Phân loại: Dữ liệu đầu vào/ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 9</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 9.
+2. Thực hiện chuỗi nghiệp vụ: Nhập KHB quân sự → Gửi chờ duyệt → Đề xuất điều chỉnh (nếu cần) → Phê duyệt → Thông báo tự động cho các bên liên quan HTSLB.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 9, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 10: Điện văn mới nhận → Lưu vào bảng inbox_current → Scheduler hàng đêm chuyển bản ghi &gt; 7 ngày sang inbox_archive → Người dùng search với date range mở rộng (≤ 60 ngày) → Hệ thống query cả 2 bảng. merge kết quả → Hiển thị/pagination như bình thường</t>
+  </si>
+  <si>
+    <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 10</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 10.
+2. Thực hiện chuỗi nghiệp vụ: Điện văn mới nhận → Lưu vào bảng inbox_current → Scheduler hàng đêm chuyển bản ghi &gt; 7 ngày sang inbox_archive → Người dùng search với date range mở rộng (≤ 60 ngày) → Hệ thống query cả 2 bảng. merge kết quả → Hiển thị/pagination như bình thường.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 10, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 11: Vượt quá 60 ngày → Tự động purge theo policy hoặc chuyển sang cold storage (object storage)</t>
+  </si>
+  <si>
+    <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 11</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 11.
+2. Thực hiện chuỗi nghiệp vụ: Vượt quá 60 ngày → Tự động purge theo policy hoặc chuyển sang cold storage (object storage).
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 11, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 12: Nhận điện văn mới (bất kỳ loại nào) → Extract flight identifier (callsign. date. route) → Query KHBN → Nếu NOT FOUND: gán flag NOPERM. đổi màu hiển thị thành đỏ → Hiển thị popup cảnh báo + ghi log → Yêu cầu operator xác nhận hoặc bổ sung phép bay</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 12</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 12.
+2. Thực hiện chuỗi nghiệp vụ: Nhận điện văn mới (bất kỳ loại nào) → Extract flight identifier (callsign. date. route) → Query KHBN → Nếu NOT FOUND: gán flag NOPERM. đổi màu hiển thị thành đỏ → Hiển thị popup cảnh báo + ghi log → Yêu cầu operator xác nhận hoặc bổ sung phép bay.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 12, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 13: Chuyến bay đặc biệt (VIP/Emergency) → Whitelist cấu hình trước. bỏ qua cảnh báo NOPERM</t>
+  </si>
+  <si>
+    <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 13</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 13.
+2. Thực hiện chuỗi nghiệp vụ: Chuyến bay đặc biệt (VIP/Emergency) → Whitelist cấu hình trước. bỏ qua cảnh báo NOPERM.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 13, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 14: Khi nhập/hiển thị FPL → Tính toán: delta = submission_time - estimated_departure_time → Nếu delta &gt; 120h hoặc delta &lt; 60 ph: cảnh báo "Ngoài khung ICAO" → Ẩn khỏi danh sách chính hoặc hiển thị với badge cảnh báo → Yêu cầu xác nhận đặc biệt nếu muốn hiển thị</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 14</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 14.
+2. Thực hiện chuỗi nghiệp vụ: Khi nhập/hiển thị FPL → Tính toán: delta = submission_time - estimated_departure_time → Nếu delta &gt; 120h hoặc delta &lt; 60 ph: cảnh báo "Ngoài khung ICAO" → Ẩn khỏi danh sách chính hoặc hiển thị với badge cảnh báo → Yêu cầu xác nhận đặc biệt nếu muốn hiển thị.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 14, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 15: FPL sửa đổi (CHG) trong khung hợp lệ → Cho phép hiển thị bình thường dù FPL gốc &gt; 120h</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 15</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 15.
+2. Thực hiện chuỗi nghiệp vụ: FPL sửa đổi (CHG) trong khung hợp lệ → Cho phép hiển thị bình thường dù FPL gốc &gt; 120h.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 15, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 16: Người dùng nhập từ khóa vào search box → Hệ thống query across fields → Áp dụng full-text search cho match thông minh → Hiển thị kết quả với \n33 highlight từ khóa match → Hỗ trợ pagination và sort theo relevance</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 16</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 16.
+2. Thực hiện chuỗi nghiệp vụ: Người dùng nhập từ khóa vào search box → Hệ thống query across fields → Áp dụng full-text search cho match thông minh → Hiển thị kết quả với \n33 highlight từ khóa match → Hỗ trợ pagination và sort theo relevance.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 16, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 17: Từ khóa quá ngắn (&lt; 2 ký tự) → Yêu cầu nhập thêm hoặc hiển thị gợi ý autocomplete</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 17</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 17.
+2. Thực hiện chuỗi nghiệp vụ: Từ khóa quá ngắn (&lt; 2 ký tự) → Yêu cầu nhập thêm hoặc hiển thị gợi ý autocomplete.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 17, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 18: Mở màn hình Advanced Search → Chọn bộ lọc: airport. date range. flight type. airline. status → Hệ thống build dynamic query → Hiển thị kết quả dạng bảng → Cho phép export CSV/Excel/PDF trực tiếp từ kết quả</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 18</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 18.
+2. Thực hiện chuỗi nghiệp vụ: Mở màn hình Advanced Search → Chọn bộ lọc: airport. date range. flight type. airline. status → Hệ thống build dynamic query → Hiển thị kết quả dạng bảng → Cho phép export CSV/Excel/PDF trực tiếp từ kết quả.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 18, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 19: Kết quả quá lớn (&gt; 10.000 records) → Cảnh báo và yêu cầu thu hẹp phạm vi hoặc export background với notification khi hoàn thành</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 19</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 19.
+2. Thực hiện chuỗi nghiệp vụ: Kết quả quá lớn (&gt; 10.000 records) → Cảnh báo và yêu cầu thu hẹp phạm vi hoặc export background với notification khi hoàn thành.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 19, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 20: Khi nhập/sửa chuyến bay → Hệ thống check phân loại domestic/international → Đề xuất phân loại tự động → Người dùng xác nhận hoặc override thủ công → Lưu metadata flight_category vào CSDL → Hiển thị badge phân loại trong UI</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 20</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 20.
+2. Thực hiện chuỗi nghiệp vụ: Khi nhập/sửa chuyến bay → Hệ thống check phân loại domestic/international → Đề xuất phân loại tự động → Người dùng xác nhận hoặc override thủ công → Lưu metadata flight_category vào CSDL → Hiển thị badge phân loại trong UI.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 20, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 21: Sân bay chưa có thông tin country → Đánh dấu UNKNOWN. yêu cầu admin bổ sung dữ liệu tham chiếu</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 21</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 21.
+2. Thực hiện chuỗi nghiệp vụ: Sân bay chưa có thông tin country → Đánh dấu UNKNOWN. yêu cầu admin bổ sung dữ liệu tham chiếu.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 21, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 22: Người dùng chọn phạm vi export → Chọn loại output: ALL/LD-only/OF- only → Hệ thống lọc dữ liệu theo tiêu chí → Sinh file riêng biệt với naming convention → Cho phép download đồng thời hoặc gửi qua email/SFTP</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 22</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 22.
+2. Thực hiện chuỗi nghiệp vụ: Người dùng chọn phạm vi export → Chọn loại output: ALL/LD-only/OF- only → Hệ thống lọc dữ liệu theo tiêu chí → Sinh file riêng biệt với naming convention → Cho phép download đồng thời hoặc gửi qua email/SFTP.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 22, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 23: Dữ liệu quá lớn → Nén file thành .zip. thông báo thời gian xử lý dự kiến</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 23</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 23.
+2. Thực hiện chuỗi nghiệp vụ: Dữ liệu quá lớn → Nén file thành .zip. thông báo thời gian xử lý dự kiến.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 23, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 24: Operator mở form Edit flight → Hệ thống load form sửa → Người dùng sửa thông tin → Validate theo rule engine → Lưu thay đổi + ghi audit log</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 24</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 24.
+2. Thực hiện chuỗi nghiệp vụ: Operator mở form Edit flight → Hệ thống load form sửa → Người dùng sửa thông tin → Validate theo rule engine → Lưu thay đổi + ghi audit log.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 24, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 25: Schema không hợp lệ → Hệ thống fallback về default form. báo lỗi cho admin</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 25</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 25.
+2. Thực hiện chuỗi nghiệp vụ: Schema không hợp lệ → Hệ thống fallback về default form. báo lỗi cho admin.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 25, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 26: Mở chi tiết chuyến bay → Chuyển sang tab "Lịch sử xử lý" → Hệ thống \n34 query audit_log theo flight_id → Hiển thị timeline → Mỗi event hiển thị: timestamp. user_name. action_type. old_value → new_value. note → Hỗ trợ filter theo user/date/action</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 26</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 26.
+2. Thực hiện chuỗi nghiệp vụ: Mở chi tiết chuyến bay → Chuyển sang tab "Lịch sử xử lý" → Hệ thống \n34 query audit_log theo flight_id → Hiển thị timeline → Mỗi event hiển thị: timestamp. user_name. action_type. old_value → new_value. note → Hỗ trợ filter theo user/date/action.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 26, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 27: Nhận điện văn DEP/ARR → Extract flight_id + event_timestamp → Nếu event_date != scheduled_date: đánh dấu cross_midnight = true → Link các điện văn theo flight_id thay vì theo ngày → Hiển thị trong UI theo ngày nghiệp vụ thực tế → Báo cáo thống kê tính đúng ngày thực tế</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 27</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 27.
+2. Thực hiện chuỗi nghiệp vụ: Nhận điện văn DEP/ARR → Extract flight_id + event_timestamp → Nếu event_date != scheduled_date: đánh dấu cross_midnight = true → Link các điện văn theo flight_id thay vì theo ngày → Hiển thị trong UI theo ngày nghiệp vụ thực tế → Báo cáo thống kê tính đúng ngày thực tế.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 27, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 28: Thiếu thông tin ngày thực tế → Dùng scheduled_date làm fallback. đánh flag date_uncertain để review sau</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 28</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 28.
+2. Thực hiện chuỗi nghiệp vụ: Thiếu thông tin ngày thực tế → Dùng scheduled_date làm fallback. đánh flag date_uncertain để review sau.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 28, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 29: Người dùng chọn tiêu chí: time_granularity. group_by. metrics → Hệ thống xử lý dữ liệu → Hiển thị biểu đồ + bảng số liệu → Cho phép xem từ tổng quan vào chi tiết → Export kết quả ra PDF/Excel</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 29</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 29.
+2. Thực hiện chuỗi nghiệp vụ: Người dùng chọn tiêu chí: time_granularity. group_by. metrics → Hệ thống xử lý dữ liệu → Hiển thị biểu đồ + bảng số liệu → Cho phép xem từ tổng quan vào chi tiết → Export kết quả ra PDF/Excel.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 29, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 30: Dữ liệu chưa đủ để thống kê → Hiển thị thông báo và gợi ý mở rộng khoảng thời gian</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 30</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 30.
+2. Thực hiện chuỗi nghiệp vụ: Dữ liệu chưa đủ để thống kê → Hiển thị thông báo và gợi ý mở rộng khoảng thời gian.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 30, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 31: So sánh danh sách bay thực tế vs KH phê duyệt → Phát hiện mismatch → Gán status UNPERMITTED. hiển thị màu đỏ → Tạo alert với mức độ HIGH → Yêu cầu xác nhận bổ sung permit hoặc giải trình → Ghi log vi phạm để báo cáo</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 31</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 31.
+2. Thực hiện chuỗi nghiệp vụ: So sánh danh sách bay thực tế vs KH phê duyệt → Phát hiện mismatch → Gán status UNPERMITTED. hiển thị màu đỏ → Tạo alert với mức độ HIGH → Yêu cầu xác nhận bổ sung permit hoặc giải trình → Ghi log vi phạm để báo cáo.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 31, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 32: Chuyến bay được phép đặc biệt (military/emergency) → Check whitelist. nếu có thì không cảnh báo</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 32</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 32.
+2. Thực hiện chuỗi nghiệp vụ: Chuyến bay được phép đặc biệt (military/emergency) → Check whitelist. nếu có thì không cảnh báo.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 32, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 33: Chọn chuyến bay → Nhấn "Hủy" → Nhập lý do hủy (mandatory) → Hệ thống cập nhật status → CANCELLED → Ghi audit log và thông báo kết quả</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 33</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 33.
+2. Thực hiện chuỗi nghiệp vụ: Chọn chuyến bay → Nhấn "Hủy" → Nhập lý do hủy (mandatory) → Hệ thống cập nhật status → CANCELLED → Ghi audit log và thông báo kết quả.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 33, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 34: Chuyến bay đã DEP → Không cho hủy. yêu cầu dùng quy trình \n35 DLA/ARR thay thế</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 34</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 34.
+2. Thực hiện chuỗi nghiệp vụ: Chuyến bay đã DEP → Không cho hủy. yêu cầu dùng quy trình \n35 DLA/ARR thay thế.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 34, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 35: User yêu cầu export Bravo → Thực hiện chuyển dữ liệu → Trả kết quả trong &lt; 60s → Ghi log</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 35</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 35.
+2. Thực hiện chuỗi nghiệp vụ: User yêu cầu export Bravo → Thực hiện chuyển dữ liệu → Trả kết quả trong &lt; 60s → Ghi log.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 35, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 36: Dataset quá lớn (&gt; 50.000 records) → Chuyển sang background job. notify khi hoàn thành qua email/popup</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 36</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 36.
+2. Thực hiện chuỗi nghiệp vụ: Dataset quá lớn (&gt; 50.000 records) → Chuyển sang background job. notify khi hoàn thành qua email/popup.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 36, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 37: Mở Calendar Accepted → Chọn chuyến bay cần điều chỉnh → Nhấn F8 → Hệ thống cho phép kéo-thả hoặc nhập vị trí dòng mới → Lưu dữ liệu hiển thị theo user/session → Hiển thị lại lịch với bố cục mới</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 37</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 37.
+2. Thực hiện chuỗi nghiệp vụ: Mở Calendar Accepted → Chọn chuyến bay cần điều chỉnh → Nhấn F8 → Hệ thống cho phép kéo-thả hoặc nhập vị trí dòng mới → Lưu dữ liệu hiển thị theo user/session → Hiển thị lại lịch với bố cục mới.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 37, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 38: Vị trí mới trùng với chuyến khác → Cảnh báo và yêu cầu chọn vị trí khác</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 38</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 38.
+2. Thực hiện chuỗi nghiệp vụ: Vị trí mới trùng với chuyến khác → Cảnh báo và yêu cầu chọn vị trí khác.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 38, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 39: Đến giờ quy định → Tạo kế hoạch bay → Hệ thống thực hiện → Ghi log → Hoàn thành toàn bộ trong &lt; 60s → Gửi thông báo "Gen KHB completed"</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 39</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 39.
+2. Thực hiện chuỗi nghiệp vụ: Đến giờ quy định → Tạo kế hoạch bay → Hệ thống thực hiện → Ghi log → Hoàn thành toàn bộ trong &lt; 60s → Gửi thông báo "Gen KHB completed".
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 39, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 40: Lỗi kết nối AMHS → Lưu messages vào local queue. retry tự động khi kết nối phục hồi</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 40</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 40.
+2. Thực hiện chuỗi nghiệp vụ: Lỗi kết nối AMHS → Lưu messages vào local queue. retry tự động khi kết nối phục hồi.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 40, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 41: Vào mục INBOX → Chọn date range: từ [date] đến [date] (tối đa 60 ngày) → Hệ thống query cả bảng current + archive → Hiển thị kết quả với pagination → Cho phép export kết quả tìm kiếm</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 41</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 41.
+2. Thực hiện chuỗi nghiệp vụ: Vào mục INBOX → Chọn date range: từ [date] đến [date] (tối đa 60 ngày) → Hệ thống query cả bảng current + archive → Hiển thị kết quả với pagination → Cho phép export kết quả tìm kiếm.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 41, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 42: Date range &gt; 60 ngày → Cảnh báo và yêu cầu thu hẹp. hoặc chuyển sang request báo cáo đặc biệt</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 42</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 42.
+2. Thực hiện chuỗi nghiệp vụ: Date range &gt; 60 ngày → Cảnh báo và yêu cầu thu hẹp. hoặc chuyển sang request báo cáo đặc biệt.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 42, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 43: Phát hiện edit request trên KHB đã build → Hệ thống kiểm tra → Cập nhật chỉ số → UI luôn hiển thị bản mới nhất. có toggle xem history → Ghi audit log thay đổi version</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 43</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 43.
+2. Thực hiện chuỗi nghiệp vụ: Phát hiện edit request trên KHB đã build → Hệ thống kiểm tra → Cập nhật chỉ số → UI luôn hiển thị bản mới nhất. có toggle xem history → Ghi audit log thay đổi version.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 43, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 44: Người dùng muốn giữ cả 2 version → Cho phép clone thành flight mới với ID khác. không ghi đè \n36</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 44</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 44.
+2. Thực hiện chuỗi nghiệp vụ: Người dùng muốn giữ cả 2 version → Cho phép clone thành flight mới với ID khác. không ghi đè \n36.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 44, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 45: Khi nhập/cập nhật permit → Tính toán ghi log</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 45</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 45.
+2. Thực hiện chuỗi nghiệp vụ: Khi nhập/cập nhật permit → Tính toán ghi log.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 45, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 46: Sai lệch do múi giờ hoặc chuyển ngày dương lịch → Hệ thống hỗ trợ convert timezone trước khi so sánh</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 46</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 46.
+2. Thực hiện chuỗi nghiệp vụ: Sai lệch do múi giờ hoặc chuyển ngày dương lịch → Hệ thống hỗ trợ convert timezone trước khi so sánh.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 46, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 47: Khi thực hiện tạo điện văn → Bổ sung mục đích (Purpose) vào thông tin điện văn được sinh ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 47</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 47.
+2. Thực hiện chuỗi nghiệp vụ: Khi thực hiện tạo điện văn → Bổ sung mục đích (Purpose) vào thông tin điện văn được sinh ra.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 47, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 48: Mục đích không có trong danh sách → Cho phép nhập custom với quyền admin. đề xuất thêm vào danh sách chuẩn</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 48</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 48.
+2. Thực hiện chuỗi nghiệp vụ: Mục đích không có trong danh sách → Cho phép nhập custom với quyền admin. đề xuất thêm vào danh sách chuẩn.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 48, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 49: Tại màn hình cập nhật phép bay → Kiểm tra ngày hiệu lực → Hiện thị "đỏ" để cảnh báo</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 49</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 49.
+2. Thực hiện chuỗi nghiệp vụ: Tại màn hình cập nhật phép bay → Kiểm tra ngày hiệu lực → Hiện thị "đỏ" để cảnh báo.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 49, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 50: Khi nhận chuyến bay từ TBHĐB → Tự động kiểm tra và cập nhật đường bay dựa trên FPL thực tế đã nộp</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 50</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 50.
+2. Thực hiện chuỗi nghiệp vụ: Khi nhận chuyến bay từ TBHĐB → Tự động kiểm tra và cập nhật đường bay dựa trên FPL thực tế đã nộp.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 50, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 51: Route string không chuẩn → đánh flag ROUTE_UNCERTAIN để kiểm tra thủ công</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 51</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 51.
+2. Thực hiện chuỗi nghiệp vụ: Route string không chuẩn → đánh flag ROUTE_UNCERTAIN để kiểm tra thủ công.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 51, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 52: Export từ danh sách chuyến bay sau khi khai thác xong → Tự động kiểm tra và đánh dấu chuyến bay chuyển ngày</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 52</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 52.
+2. Thực hiện chuỗi nghiệp vụ: Export từ danh sách chuyến bay sau khi khai thác xong → Tự động kiểm tra và đánh dấu chuyến bay chuyển ngày.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 52, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 53: Mở màn hình Daily Plan → Hệ thống load baseline KHBN → Khi có chuyến bay mới được thêm: hiển thị badge "NEW". highlight row → Counter hiển thị: +X flights added → Cho phép filter → Audit log ghi nhận</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 53</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 53.
+2. Thực hiện chuỗi nghiệp vụ: Mở màn hình Daily Plan → Hệ thống load baseline KHBN → Khi có chuyến bay mới được thêm: hiển thị badge "NEW". highlight row → Counter hiển thị: +X flights added → Cho phép filter → Audit log ghi nhận.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 53, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 54: Hệ thống nhận dữ liệu từ Trung tâm TBHĐB → Hiển thị thông báo trên Dashboard → Cho phép click để xem chi tiết danh sách chuyến vừa cập nhật → Ghi log</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 54</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 54.
+2. Thực hiện chuỗi nghiệp vụ: Hệ thống nhận dữ liệu từ Trung tâm TBHĐB → Hiển thị thông báo trên Dashboard → Cho phép click để xem chi tiết danh sách chuyến vừa cập nhật → Ghi log.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 54, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 55: Chức năng đồng bộ sang Bravo → Với mỗi chuyến bay kiểm tra → Nếu tồn tại: UPDATE chỉ các trường thay đổi. KEEP ORIGINAL → Nếu \n37 không tồn tại: INSERT new record → Ghi log sync result → Gửi notification khi hoàn thành</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 55</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 55.
+2. Thực hiện chuỗi nghiệp vụ: Chức năng đồng bộ sang Bravo → Với mỗi chuyến bay kiểm tra → Nếu tồn tại: UPDATE chỉ các trường thay đổi. KEEP ORIGINAL → Nếu \n37 không tồn tại: INSERT new record → Ghi log sync result → Gửi notification khi hoàn thành.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 55, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 56: Xung đột dữ liệu (Bravo đã sửa manual) → Áp dụng policy manual_override_wins hoặc đưa vào conflict queue để review</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 56</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 56.
+2. Thực hiện chuỗi nghiệp vụ: Xung đột dữ liệu (Bravo đã sửa manual) → Áp dụng policy manual_override_wins hoặc đưa vào conflict queue để review.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 56, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 57: Khi nhận chuyến bay từ TBHĐB → Kiểm tra ngày → Cập nhật đúng ngày thực tế</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 57</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 57.
+2. Thực hiện chuỗi nghiệp vụ: Khi nhận chuyến bay từ TBHĐB → Kiểm tra ngày → Cập nhật đúng ngày thực tế.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 57, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 58: Trên danh sách chuyến bay. chọn nhiều dòng → Chọn field cần sửa → Nhập giá trị mới → Preview changes → Confirm → Hệ thống thực hiện batch update với transaction → Hiển thị kết quả → Ghi log cho từng chuyến bay</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 58</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 58.
+2. Thực hiện chuỗi nghiệp vụ: Trên danh sách chuyến bay. chọn nhiều dòng → Chọn field cần sửa → Nhập giá trị mới → Preview changes → Confirm → Hệ thống thực hiện batch update với transaction → Hiển thị kết quả → Ghi log cho từng chuyến bay.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 58, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 59: Một số flight không đủ quyền sửa → Bỏ qua những flight đó. cập nhật những flight hợp lệ. báo cáo chi tiết</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 59</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 59.
+2. Thực hiện chuỗi nghiệp vụ: Một số flight không đủ quyền sửa → Bỏ qua những flight đó. cập nhật những flight hợp lệ. báo cáo chi tiết.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 59, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 60: Chọn phạm vi đối chiếu → Hệ thống fetch data từ cả 2 nguồn → Match records → So sánh fields → Highlight mismatches → Sinh báo cáo đối chiếu → Cho phép export discrepancy list để xử lý</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 60</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 60.
+2. Thực hiện chuỗi nghiệp vụ: Chọn phạm vi đối chiếu → Hệ thống fetch data từ cả 2 nguồn → Match records → So sánh fields → Highlight mismatches → Sinh báo cáo đối chiếu → Cho phép export discrepancy list để xử lý.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 60, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 61: Không tìm thấy match key → Đánh dấu ORPHAN ở cả 2 phía. đề xuất kiểm tra dữ liệu nguồn</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 61</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 61.
+2. Thực hiện chuỗi nghiệp vụ: Không tìm thấy match key → Đánh dấu ORPHAN ở cả 2 phía. đề xuất kiểm tra dữ liệu nguồn.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 61, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 62: Mở Daily Military Report → Click vào search bar → Nhập từ khóa hoặc chọn field-specific filter → Hệ thống query với full-text search → Hiển thị kết quả với highlight match → Cho phép save search criteria → Export kết quả</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 62</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 62.
+2. Thực hiện chuỗi nghiệp vụ: Mở Daily Military Report → Click vào search bar → Nhập từ khóa hoặc chọn field-specific filter → Hệ thống query với full-text search → Hiển thị kết quả với highlight match → Cho phép save search criteria → Export kết quả.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 62, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 63: Mở bất kỳ báo cáo nào → Hiển thị panel filters với tất cả criteria → Người dùng chọn/combine nhiều criteria → Hệ thống build dynamic query → Hiển thị kết quả với option show/hide columns → Cho phép save filter \n38 preset → Export</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 63</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 63.
+2. Thực hiện chuỗi nghiệp vụ: Mở bất kỳ báo cáo nào → Hiển thị panel filters với tất cả criteria → Người dùng chọn/combine nhiều criteria → Hệ thống build dynamic query → Hiển thị kết quả với option show/hide columns → Cho phép save filter \n38 preset → Export.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 63, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 64: Người dùng truy cập Dashboard → Hệ thống hiện thị: tổng chuyến bay. tỷ lệ on-time. delay distribution. airport heatmap → Dữ liệu auto-refresh → Cho phép click để xem chi tiết → Hỗ trợ tùy chỉnh layout</t>
+  </si>
+  <si>
+    <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 64</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 64.
+2. Thực hiện chuỗi nghiệp vụ: Người dùng truy cập Dashboard → Hệ thống hiện thị: tổng chuyến bay. tỷ lệ on-time. delay distribution. airport heatmap → Dữ liệu auto-refresh → Cho phép click để xem chi tiết → Hỗ trợ tùy chỉnh layout.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 64, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 65: Mất kết nối dữ liệu real-time → Hiển thị thông báo "Dữ liệu cập nhật lúc HH:mm"</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 65</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 65.
+2. Thực hiện chuỗi nghiệp vụ: Mất kết nối dữ liệu real-time → Hiển thị thông báo "Dữ liệu cập nhật lúc HH:mm".
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 65, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 66: Chọn chỉ số phân tích → Chọn granularity → Hệ thống tính toán trend line. moving average. seasonality → Hiển thị biểu đồ với confidence interval → Dự báo ngắn hạn → Export kết quả phân tích</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 66</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 66.
+2. Thực hiện chuỗi nghiệp vụ: Chọn chỉ số phân tích → Chọn granularity → Hệ thống tính toán trend line. moving average. seasonality → Hiển thị biểu đồ với confidence interval → Dự báo ngắn hạn → Export kết quả phân tích.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 66, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 67: Engine giám sát luồng dữ liệu mới → So sánh với statistical baseline → Nếu giá trị vượt ngưỡng: đánh dấu ANOMALY → Phân loại nguyên nhân → Gửi alert → Ghi log để huấn luyện mô hình</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 67</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 67.
+2. Thực hiện chuỗi nghiệp vụ: Engine giám sát luồng dữ liệu mới → So sánh với statistical baseline → Nếu giá trị vượt ngưỡng: đánh dấu ANOMALY → Phân loại nguyên nhân → Gửi alert → Ghi log để huấn luyện mô hình.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 67, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 68: Bất thường được xác nhận là hợp lệ → Đánh dấu VALIDATED. cập nhật baseline để không cảnh báo lặp</t>
+  </si>
+  <si>
+    <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu vào</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 68</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 68.
+2. Thực hiện chuỗi nghiệp vụ: Bất thường được xác nhận là hợp lệ → Đánh dấu VALIDATED. cập nhật baseline để không cảnh báo lặp.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 68, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 69: Người dùng chọn tiêu chí báo cáo O/F → Hệ thống query ADS-B tracks đã correlate → Tính toán metrics → So sánh với planned values → Sinh báo cáo dạng bảng + biểu đồ → Export PDF/Excel/CSV</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 69</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 69.
+2. Thực hiện chuỗi nghiệp vụ: Người dùng chọn tiêu chí báo cáo O/F → Hệ thống query ADS-B tracks đã correlate → Tính toán metrics → So sánh với planned values → Sinh báo cáo dạng bảng + biểu đồ → Export PDF/Excel/CSV.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 69, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 70: Thiếu dữ liệu ADS-B cho một số chuyến → Đánh dấu PARTIAL_DATA. hiển thị cảnh báo và vẫn báo cáo với dữ liệu có sẵn</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 70</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 70.
+2. Thực hiện chuỗi nghiệp vụ: Thiếu dữ liệu ADS-B cho một số chuyến → Đánh dấu PARTIAL_DATA. hiển thị cảnh báo và vẫn báo cáo với dữ liệu có sẵn.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 70, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 71: Chọn bộ KPIs → Hệ thống aggregate theo dimension → Tính toán benchmark → Hiển thị ranking. heatmap. trend comparison → Cho phép drill-down từ aggregate vào chi tiết từng chuyến</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 71</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 71.
+2. Thực hiện chuỗi nghiệp vụ: Chọn bộ KPIs → Hệ thống aggregate theo dimension → Tính toán benchmark → Hiển thị ranking. heatmap. trend comparison → Cho phép drill-down từ aggregate vào chi tiết từng chuyến.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 71, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 72: Người dùng chọn phạm vi → Hệ thống aggregate → Tính tỷ lệ % → Hiển \n39 thị pie chart + bar chart kép → Cho phép toggle → Hover để xem chi tiết số liệu → Export hình ảnh hoặc dữ liệu</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 72</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 72.
+2. Thực hiện chuỗi nghiệp vụ: Người dùng chọn phạm vi → Hệ thống aggregate → Tính tỷ lệ % → Hiển \n39 thị pie chart + bar chart kép → Cho phép toggle → Hover để xem chi tiết số liệu → Export hình ảnh hoặc dữ liệu.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 72, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 73: Chọn nhóm sân bay so sánh → Chọn granularity thời gian → Chọn metrics → Hệ thống tính toán → Hiển thị grouped bar chart → Highlight sân bay có biến động → Export báo cáo so sánh</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 73</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 73.
+2. Thực hiện chuỗi nghiệp vụ: Chọn nhóm sân bay so sánh → Chọn granularity thời gian → Chọn metrics → Hệ thống tính toán → Hiển thị grouped bar chart → Highlight sân bay có biến động → Export báo cáo so sánh.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 73, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 74: Mở báo cáo Military Flight → Chọn criteria → Hệ thống aggregate → Hiển thị bảng + biểu đồ → Cho phép drill-down → Export PDF/Excel với watermark</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 74</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 74.
+2. Thực hiện chuỗi nghiệp vụ: Mở báo cáo Military Flight → Chọn criteria → Hệ thống aggregate → Hiển thị bảng + biểu đồ → Cho phép drill-down → Export PDF/Excel với watermark.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 74, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 75: Mở báo cáo Consolidated Airport Report → Chọn filters linh hoạt TỔNG HỢP SỐ LIỆU TỰ ĐỘNG</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 75</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 75.
+2. Thực hiện chuỗi nghiệp vụ: Mở báo cáo Consolidated Airport Report → Chọn filters linh hoạt TỔNG HỢP SỐ LIỆU TỰ ĐỘNG.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 75, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 76: Người dùng nhập câu hỏi → Chatbot tokenize và phân tích cú pháp → Nhận diện intent + entities → Map sang query cấu trúc → Chuyển truy vấn sang module xử lý dữ liệu → Nhận kết quả và sinh câu trả lời tự nhiên → Hiển thị kèm formatted data</t>
+  </si>
+  <si>
+    <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu vào/ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 76</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 76.
+2. Thực hiện chuỗi nghiệp vụ: Người dùng nhập câu hỏi → Chatbot tokenize và phân tích cú pháp → Nhận diện intent + entities → Map sang query cấu trúc → Chuyển truy vấn sang module xử lý dữ liệu → Nhận kết quả và sinh câu trả lời tự nhiên → Hiển thị kèm formatted data.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 76, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 77: Câu hỏi mơ hồ hoặc thiếu thông tin → Chatbot hỏi lại làm rõ hoặc đề xuất các lựa chọn phổ biến</t>
+  </si>
+  <si>
+    <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu ra</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 77</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 77.
+2. Thực hiện chuỗi nghiệp vụ: Câu hỏi mơ hồ hoặc thiếu thông tin → Chatbot hỏi lại làm rõ hoặc đề xuất các lựa chọn phổ biến.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 77, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 78: Nhận query object → Query Builder sinh SQL/API call → Thực thi truy vấn → Nếu kết quả lớn: áp dụng aggregation → Format kết quả thành JSON → Chuyển sang module sinh câu trả lời</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 78</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 78.
+2. Thực hiện chuỗi nghiệp vụ: Nhận query object → Query Builder sinh SQL/API call → Thực thi truy vấn → Nếu kết quả lớn: áp dụng aggregation → Format kết quả thành JSON → Chuyển sang module sinh câu trả lời.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 78, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 79: Truy vấn quá phức tạp hoặc tốn tài nguyên → Hệ thống đề xuất giới hạn phạm vi hoặc chạy background với notification khi hoàn thành</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 79</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 79.
+2. Thực hiện chuỗi nghiệp vụ: Truy vấn quá phức tạp hoặc tốn tài nguyên → Hệ thống đề xuất giới hạn phạm vi hoặc chạy background với notification khi hoàn thành.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 79, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 80: Thêm chat icon cố định ở góc màn hình → Khi click: mở chat panel → Hiển thị welcome message → Hỗ trợ input: text + voice + quick-reply \n40 buttons → Kết quả hiển thị trong chat → Hỗ trợ keyboard shortcut</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 80</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 80.
+2. Thực hiện chuỗi nghiệp vụ: Thêm chat icon cố định ở góc màn hình → Khi click: mở chat panel → Hiển thị welcome message → Hỗ trợ input: text + voice + quick-reply \n40 buttons → Kết quả hiển thị trong chat → Hỗ trợ keyboard shortcut.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 80, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 81: User đang làm việc với form quan trọng → Chatbot không auto-popup. chỉ hiển thị badge notification khi có alert quan trọng</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 81</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 81.
+2. Thực hiện chuỗi nghiệp vụ: User đang làm việc với form quan trọng → Chatbot không auto-popup. chỉ hiển thị badge notification khi có alert quan trọng.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 81, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>Yêu cầu Bảng 1 số 82: Thu thập metrics: số câu hỏi/ngày. tỷ lệ các loại truy vấn. % query được xử lý đúng ngay lần đầu</t>
+  </si>
+  <si>
+    <t>Kiểm thử yêu cầu Bảng 1 số 82</t>
+  </si>
+  <si>
+    <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 82.
+2. Thực hiện chuỗi nghiệp vụ: Thu thập metrics: số câu hỏi/ngày. tỷ lệ các loại truy vấn. % query được xử lý đúng ngay lần đầu.
+3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực hiện đúng yêu cầu số 82, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1507,8 +1776,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1517,12 +1784,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1546,6 +1807,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1563,7 +1832,11 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
@@ -1759,26 +2032,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2026\QLB\TrienKhai\ATFM_WEB\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Trang tính1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="152511"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1959,3721 +2213,2571 @@
       <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="33" t="s">
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="34" t="s">
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="30" t="s">
         <v>21</v>
       </c>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" ht="153" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 1: System kiểm tra thư mục theo lịch trình → Phát hiện file mới → Validate định dạng → Parse dữ liệu → Cập nhật vào CSDL → Ghi log và thông báo kết quả</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 1</t>
-        </is>
-      </c>
-      <c r="E6" s="38" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 1.
-2. Thực hiện chuỗi nghiệp vụ: System kiểm tra thư mục theo lịch trình → Phát hiện file mới → Validate định dạng → Parse dữ liệu → Cập nhật vào CSDL → Ghi log và thông báo kết quả.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 1, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="28"/>
+    <row r="6" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="26"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="26"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 2: File lỗi định dạng → Hệ thống chuyển vào thư mục error và gửi cảnh báo cho Admin</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D7" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 2</t>
-        </is>
-      </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 2.
-2. Thực hiện chuỗi nghiệp vụ: File lỗi định dạng → Hệ thống chuyển vào thư mục error và gửi cảnh báo cho Admin.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F7" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 2, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="28"/>
+    <row r="7" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A7" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="26"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 3: Nhận file dữ liệu ADS-B → Match với kế hoạch bay → Cập nhật trạng thái O/F → Hiển thị real-time trên map/dashboard</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D8" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 3</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 3.
-2. Thực hiện chuỗi nghiệp vụ: Nhận file dữ liệu ADS-B → Match với kế hoạch bay → Cập nhật trạng thái O/F → Hiển thị real-time trên map/dashboard.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 3, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28"/>
+    <row r="8" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 4: Nhập thông tin chuyến bay SLOT → Nhập thông tin kế hoạch ngày của hãng → Kiểm tra trùng/khả dụng → Đưa ra danh sách chuyên bay không diễn ra → Xác nhận và lưu vào kế hoạch</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 4</t>
-        </is>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 4.
-2. Thực hiện chuỗi nghiệp vụ: Nhập thông tin chuyến bay SLOT → Nhập thông tin kế hoạch ngày của hãng → Kiểm tra trùng/khả dụng → Đưa ra danh sách chuyên bay không diễn ra → Xác nhận và lưu vào kế hoạch.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 4, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
+    <row r="9" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
       <c r="Q9" s="1"/>
     </row>
-    <row r="10" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 5: Hệ thống truy cập vào cơ sở dữ liệu điện văn của AMHS → Đọc và phân tích điện văn → Cập nhật trạng thái và lưu log</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D10" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 5</t>
-        </is>
-      </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 5.
-2. Thực hiện chuỗi nghiệp vụ: Hệ thống truy cập vào cơ sở dữ liệu điện văn của AMHS → Đọc và phân tích điện văn → Cập nhật trạng thái và lưu log.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 5, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="28"/>
+    <row r="10" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="26"/>
       <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" ht="102" x14ac:dyDescent="0.2">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 6: Hệ thống xuất dữ liệu điện văn vào bảng cơ sở dữ liệu điện văn của AMHS → Cập nhật trạng thái và lưu log</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D11" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 6</t>
-        </is>
-      </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 6.
-2. Thực hiện chuỗi nghiệp vụ: Hệ thống xuất dữ liệu điện văn vào bảng cơ sở dữ liệu điện văn của AMHS → Cập nhật trạng thái và lưu log.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 6, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
+      <c r="A11" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 7: Client gửi request với token → API Gateway validate → Router đến service tương ứng → Trả về dữ liệu định dạng JSON → Ghi audit log</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 1: TÍCH HỢP &amp; TỰ ĐỘNG HÓA DỮ LIỆU; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 7</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 7.
-2. Thực hiện chuỗi nghiệp vụ: Client gửi request với token → API Gateway validate → Router đến service tương ứng → Trả về dữ liệu định dạng JSON → Ghi audit log.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 7, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
+    <row r="12" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 8: Engine giám sát sự kiện thời gian thực → So sánh với rule set → Kích hoạt cảnh báo khi match → Gửi notification → Ghi nhận trạng thái xử lý \n32</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 2: CẢNH BÁO &amp; TIỆN ÍCH HỖ TRỢ; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D13" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 8</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 8.
-2. Thực hiện chuỗi nghiệp vụ: Engine giám sát sự kiện thời gian thực → So sánh với rule set → Kích hoạt cảnh báo khi match → Gửi notification → Ghi nhận trạng thái xử lý \n32.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F13" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 8, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
+      <c r="A13" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 9: Nhập KHB quân sự → Gửi chờ duyệt → Đề xuất điều chỉnh (nếu cần) → Phê duyệt → Thông báo tự động cho các bên liên quan HTSLB</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 2: CẢNH BÁO &amp; TIỆN ÍCH HỖ TRỢ; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D14" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 9</t>
-        </is>
-      </c>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 9.
-2. Thực hiện chuỗi nghiệp vụ: Nhập KHB quân sự → Gửi chờ duyệt → Đề xuất điều chỉnh (nếu cần) → Phê duyệt → Thông báo tự động cho các bên liên quan HTSLB.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F14" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 9, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
+      <c r="A14" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
       <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 10: Điện văn mới nhận → Lưu vào bảng inbox_current → Scheduler hàng đêm chuyển bản ghi &gt; 7 ngày sang inbox_archive → Người dùng search với date range mở rộng (≤ 60 ngày) → Hệ thống query cả 2 bảng. merge kết quả → Hiển thị/pagination như bình thường</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D15" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 10</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 10.
-2. Thực hiện chuỗi nghiệp vụ: Điện văn mới nhận → Lưu vào bảng inbox_current → Scheduler hàng đêm chuyển bản ghi &gt; 7 ngày sang inbox_archive → Người dùng search với date range mở rộng (≤ 60 ngày) → Hệ thống query cả 2 bảng. merge kết quả → Hiển thị/pagination như bình thường.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F15" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 10, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
+      <c r="A15" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="35" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B16" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 11: Vượt quá 60 ngày → Tự động purge theo policy hoặc chuyển sang cold storage (object storage)</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 11</t>
-        </is>
-      </c>
-      <c r="E16" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 11.
-2. Thực hiện chuỗi nghiệp vụ: Vượt quá 60 ngày → Tự động purge theo policy hoặc chuyển sang cold storage (object storage).
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 11, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
+      <c r="A16" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 12: Nhận điện văn mới (bất kỳ loại nào) → Extract flight identifier (callsign. date. route) → Query KHBN → Nếu NOT FOUND: gán flag NOPERM. đổi màu hiển thị thành đỏ → Hiển thị popup cảnh báo + ghi log → Yêu cầu operator xác nhận hoặc bổ sung phép bay</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D17" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 12</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 12.
-2. Thực hiện chuỗi nghiệp vụ: Nhận điện văn mới (bất kỳ loại nào) → Extract flight identifier (callsign. date. route) → Query KHBN → Nếu NOT FOUND: gán flag NOPERM. đổi màu hiển thị thành đỏ → Hiển thị popup cảnh báo + ghi log → Yêu cầu operator xác nhận hoặc bổ sung phép bay.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 12, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="28"/>
+      <c r="A17" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 13: Chuyến bay đặc biệt (VIP/Emergency) → Whitelist cấu hình trước. bỏ qua cảnh báo NOPERM</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D18" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 13</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 13.
-2. Thực hiện chuỗi nghiệp vụ: Chuyến bay đặc biệt (VIP/Emergency) → Whitelist cấu hình trước. bỏ qua cảnh báo NOPERM.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 13, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
+      <c r="A18" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
       <c r="Q18" s="1"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 14: Khi nhập/hiển thị FPL → Tính toán: delta = submission_time - estimated_departure_time → Nếu delta &gt; 120h hoặc delta &lt; 60 ph: cảnh báo "Ngoài khung ICAO" → Ẩn khỏi danh sách chính hoặc hiển thị với badge cảnh báo → Yêu cầu xác nhận đặc biệt nếu muốn hiển thị</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D19" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 14</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 14.
-2. Thực hiện chuỗi nghiệp vụ: Khi nhập/hiển thị FPL → Tính toán: delta = submission_time - estimated_departure_time → Nếu delta &gt; 120h hoặc delta &lt; 60 ph: cảnh báo "Ngoài khung ICAO" → Ẩn khỏi danh sách chính hoặc hiển thị với badge cảnh báo → Yêu cầu xác nhận đặc biệt nếu muốn hiển thị.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F19" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 14, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
+      <c r="A19" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 15: FPL sửa đổi (CHG) trong khung hợp lệ → Cho phép hiển thị bình thường dù FPL gốc &gt; 120h</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D20" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 15</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 15.
-2. Thực hiện chuỗi nghiệp vụ: FPL sửa đổi (CHG) trong khung hợp lệ → Cho phép hiển thị bình thường dù FPL gốc &gt; 120h.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F20" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 15, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
+      <c r="A20" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 16: Người dùng nhập từ khóa vào search box → Hệ thống query across fields → Áp dụng full-text search cho match thông minh → Hiển thị kết quả với \n33 highlight từ khóa match → Hỗ trợ pagination và sort theo relevance</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D21" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 16</t>
-        </is>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 16.
-2. Thực hiện chuỗi nghiệp vụ: Người dùng nhập từ khóa vào search box → Hệ thống query across fields → Áp dụng full-text search cho match thông minh → Hiển thị kết quả với \n33 highlight từ khóa match → Hỗ trợ pagination và sort theo relevance.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F21" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 16, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="28"/>
+    <row r="21" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
       <c r="Q21" s="1"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 17: Từ khóa quá ngắn (&lt; 2 ký tự) → Yêu cầu nhập thêm hoặc hiển thị gợi ý autocomplete</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D22" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 17</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 17.
-2. Thực hiện chuỗi nghiệp vụ: Từ khóa quá ngắn (&lt; 2 ký tự) → Yêu cầu nhập thêm hoặc hiển thị gợi ý autocomplete.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F22" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 17, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
+    <row r="22" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A22" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
       <c r="Q22" s="1"/>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B23" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 18: Mở màn hình Advanced Search → Chọn bộ lọc: airport. date range. flight type. airline. status → Hệ thống build dynamic query → Hiển thị kết quả dạng bảng → Cho phép export CSV/Excel/PDF trực tiếp từ kết quả</t>
-        </is>
-      </c>
-      <c r="C23" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 18</t>
-        </is>
-      </c>
-      <c r="E23" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 18.
-2. Thực hiện chuỗi nghiệp vụ: Mở màn hình Advanced Search → Chọn bộ lọc: airport. date range. flight type. airline. status → Hệ thống build dynamic query → Hiển thị kết quả dạng bảng → Cho phép export CSV/Excel/PDF trực tiếp từ kết quả.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F23" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 18, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
+      <c r="A23" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
       <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 19: Kết quả quá lớn (&gt; 10.000 records) → Cảnh báo và yêu cầu thu hẹp phạm vi hoặc export background với notification khi hoàn thành</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D24" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 19</t>
-        </is>
-      </c>
-      <c r="E24" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 19.
-2. Thực hiện chuỗi nghiệp vụ: Kết quả quá lớn (&gt; 10.000 records) → Cảnh báo và yêu cầu thu hẹp phạm vi hoặc export background với notification khi hoàn thành.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 19, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
+    <row r="24" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 20: Khi nhập/sửa chuyến bay → Hệ thống check phân loại domestic/international → Đề xuất phân loại tự động → Người dùng xác nhận hoặc override thủ công → Lưu metadata flight_category vào CSDL → Hiển thị badge phân loại trong UI</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D25" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 20</t>
-        </is>
-      </c>
-      <c r="E25" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 20.
-2. Thực hiện chuỗi nghiệp vụ: Khi nhập/sửa chuyến bay → Hệ thống check phân loại domestic/international → Đề xuất phân loại tự động → Người dùng xác nhận hoặc override thủ công → Lưu metadata flight_category vào CSDL → Hiển thị badge phân loại trong UI.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F25" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 20, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="28"/>
+    <row r="25" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="26"/>
       <c r="Q25" s="1"/>
     </row>
     <row r="26" spans="1:17" ht="102" x14ac:dyDescent="0.2">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 21: Sân bay chưa có thông tin country → Đánh dấu UNKNOWN. yêu cầu admin bổ sung dữ liệu tham chiếu</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D26" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 21</t>
-        </is>
-      </c>
-      <c r="E26" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 21.
-2. Thực hiện chuỗi nghiệp vụ: Sân bay chưa có thông tin country → Đánh dấu UNKNOWN. yêu cầu admin bổ sung dữ liệu tham chiếu.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 21, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="29" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 22: Người dùng chọn phạm vi export → Chọn loại output: ALL/LD-only/OF- only → Hệ thống lọc dữ liệu theo tiêu chí → Sinh file riêng biệt với naming convention → Cho phép download đồng thời hoặc gửi qua email/SFTP</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D27" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 22</t>
-        </is>
-      </c>
-      <c r="E27" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 22.
-2. Thực hiện chuỗi nghiệp vụ: Người dùng chọn phạm vi export → Chọn loại output: ALL/LD-only/OF- only → Hệ thống lọc dữ liệu theo tiêu chí → Sinh file riêng biệt với naming convention → Cho phép download đồng thời hoặc gửi qua email/SFTP.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F27" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 22, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
+    <row r="27" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 23: Dữ liệu quá lớn → Nén file thành .zip. thông báo thời gian xử lý dự kiến</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D28" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 23</t>
-        </is>
-      </c>
-      <c r="E28" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 23.
-2. Thực hiện chuỗi nghiệp vụ: Dữ liệu quá lớn → Nén file thành .zip. thông báo thời gian xử lý dự kiến.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 23, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
+    <row r="28" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A28" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="29" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 24: Operator mở form Edit flight → Hệ thống load form sửa → Người dùng sửa thông tin → Validate theo rule engine → Lưu thay đổi + ghi audit log</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D29" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 24</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 24.
-2. Thực hiện chuỗi nghiệp vụ: Operator mở form Edit flight → Hệ thống load form sửa → Người dùng sửa thông tin → Validate theo rule engine → Lưu thay đổi + ghi audit log.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 24, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
+    <row r="29" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 25: Schema không hợp lệ → Hệ thống fallback về default form. báo lỗi cho admin</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D30" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 25</t>
-        </is>
-      </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 25.
-2. Thực hiện chuỗi nghiệp vụ: Schema không hợp lệ → Hệ thống fallback về default form. báo lỗi cho admin.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 25, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28"/>
+    <row r="30" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A30" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
       <c r="Q30" s="1"/>
     </row>
-    <row r="31" spans="1:17" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="29" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 26: Mở chi tiết chuyến bay → Chuyển sang tab "Lịch sử xử lý" → Hệ thống \n34 query audit_log theo flight_id → Hiển thị timeline → Mỗi event hiển thị: timestamp. user_name. action_type. old_value → new_value. note → Hỗ trợ filter theo user/date/action</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D31" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 26</t>
-        </is>
-      </c>
-      <c r="E31" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 26.
-2. Thực hiện chuỗi nghiệp vụ: Mở chi tiết chuyến bay → Chuyển sang tab "Lịch sử xử lý" → Hệ thống \n34 query audit_log theo flight_id → Hiển thị timeline → Mỗi event hiển thị: timestamp. user_name. action_type. old_value → new_value. note → Hỗ trợ filter theo user/date/action.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 26, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
+    <row r="31" spans="1:17" ht="153" x14ac:dyDescent="0.2">
+      <c r="A31" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 27: Nhận điện văn DEP/ARR → Extract flight_id + event_timestamp → Nếu event_date != scheduled_date: đánh dấu cross_midnight = true → Link các điện văn theo flight_id thay vì theo ngày → Hiển thị trong UI theo ngày nghiệp vụ thực tế → Báo cáo thống kê tính đúng ngày thực tế</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D32" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 27</t>
-        </is>
-      </c>
-      <c r="E32" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 27.
-2. Thực hiện chuỗi nghiệp vụ: Nhận điện văn DEP/ARR → Extract flight_id + event_timestamp → Nếu event_date != scheduled_date: đánh dấu cross_midnight = true → Link các điện văn theo flight_id thay vì theo ngày → Hiển thị trong UI theo ngày nghiệp vụ thực tế → Báo cáo thống kê tính đúng ngày thực tế.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 27, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
+    <row r="32" spans="1:17" ht="153" x14ac:dyDescent="0.2">
+      <c r="A32" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A33" s="35" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B33" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 28: Thiếu thông tin ngày thực tế → Dùng scheduled_date làm fallback. đánh flag date_uncertain để review sau</t>
-        </is>
-      </c>
-      <c r="C33" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 28</t>
-        </is>
-      </c>
-      <c r="E33" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 28.
-2. Thực hiện chuỗi nghiệp vụ: Thiếu thông tin ngày thực tế → Dùng scheduled_date làm fallback. đánh flag date_uncertain để review sau.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 28, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
+    <row r="33" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A33" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A34" s="29" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 29: Người dùng chọn tiêu chí: time_granularity. group_by. metrics → Hệ thống xử lý dữ liệu → Hiển thị biểu đồ + bảng số liệu → Cho phép xem từ tổng quan vào chi tiết → Export kết quả ra PDF/Excel</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D34" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 29</t>
-        </is>
-      </c>
-      <c r="E34" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 29.
-2. Thực hiện chuỗi nghiệp vụ: Người dùng chọn tiêu chí: time_granularity. group_by. metrics → Hệ thống xử lý dữ liệu → Hiển thị biểu đồ + bảng số liệu → Cho phép xem từ tổng quan vào chi tiết → Export kết quả ra PDF/Excel.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 29, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
+    <row r="34" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
       <c r="Q34" s="1"/>
     </row>
-    <row r="35" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A35" s="29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 30: Dữ liệu chưa đủ để thống kê → Hiển thị thông báo và gợi ý mở rộng khoảng thời gian</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D35" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 30</t>
-        </is>
-      </c>
-      <c r="E35" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 30.
-2. Thực hiện chuỗi nghiệp vụ: Dữ liệu chưa đủ để thống kê → Hiển thị thông báo và gợi ý mở rộng khoảng thời gian.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 30, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
+    <row r="35" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A35" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A36" s="29" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 31: So sánh danh sách bay thực tế vs KH phê duyệt → Phát hiện mismatch → Gán status UNPERMITTED. hiển thị màu đỏ → Tạo alert với mức độ HIGH → Yêu cầu xác nhận bổ sung permit hoặc giải trình → Ghi log vi phạm để báo cáo</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D36" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 31</t>
-        </is>
-      </c>
-      <c r="E36" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 31.
-2. Thực hiện chuỗi nghiệp vụ: So sánh danh sách bay thực tế vs KH phê duyệt → Phát hiện mismatch → Gán status UNPERMITTED. hiển thị màu đỏ → Tạo alert với mức độ HIGH → Yêu cầu xác nhận bổ sung permit hoặc giải trình → Ghi log vi phạm để báo cáo.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F36" s="39" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 31, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="28"/>
+    <row r="36" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A36" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="F36" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="26"/>
       <c r="Q36" s="1"/>
     </row>
-    <row r="37" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A37" s="29" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 32: Chuyến bay được phép đặc biệt (military/emergency) → Check whitelist. nếu có thì không cảnh báo</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D37" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 32</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 32.
-2. Thực hiện chuỗi nghiệp vụ: Chuyến bay được phép đặc biệt (military/emergency) → Check whitelist. nếu có thì không cảnh báo.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F37" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 32, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
+    <row r="37" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A37" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A38" s="35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B38" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 33: Chọn chuyến bay → Nhấn "Hủy" → Nhập lý do hủy (mandatory) → Hệ thống cập nhật status → CANCELLED → Ghi audit log và thông báo kết quả</t>
-        </is>
-      </c>
-      <c r="C38" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D38" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 33</t>
-        </is>
-      </c>
-      <c r="E38" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 33.
-2. Thực hiện chuỗi nghiệp vụ: Chọn chuyến bay → Nhấn "Hủy" → Nhập lý do hủy (mandatory) → Hệ thống cập nhật status → CANCELLED → Ghi audit log và thông báo kết quả.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 33, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
+    <row r="38" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A38" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="29" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 34: Chuyến bay đã DEP → Không cho hủy. yêu cầu dùng quy trình \n35 DLA/ARR thay thế</t>
-        </is>
-      </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D39" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 34</t>
-        </is>
-      </c>
-      <c r="E39" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 34.
-2. Thực hiện chuỗi nghiệp vụ: Chuyến bay đã DEP → Không cho hủy. yêu cầu dùng quy trình \n35 DLA/ARR thay thế.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 34, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
+    <row r="39" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A39" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
       <c r="Q39" s="1"/>
     </row>
-    <row r="40" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B40" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 35: User yêu cầu export Bravo → Thực hiện chuyển dữ liệu → Trả kết quả trong &lt; 60s → Ghi log</t>
-        </is>
-      </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D40" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 35</t>
-        </is>
-      </c>
-      <c r="E40" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 35.
-2. Thực hiện chuỗi nghiệp vụ: User yêu cầu export Bravo → Thực hiện chuyển dữ liệu → Trả kết quả trong &lt; 60s → Ghi log.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 35, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
+    <row r="40" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A40" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="26"/>
       <c r="Q40" s="1"/>
     </row>
-    <row r="41" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A41" s="29" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 36: Dataset quá lớn (&gt; 50.000 records) → Chuyển sang background job. notify khi hoàn thành qua email/popup</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D41" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 36</t>
-        </is>
-      </c>
-      <c r="E41" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 36.
-2. Thực hiện chuỗi nghiệp vụ: Dataset quá lớn (&gt; 50.000 records) → Chuyển sang background job. notify khi hoàn thành qua email/popup.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 36, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
+    <row r="41" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A41" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
       <c r="Q41" s="1"/>
     </row>
-    <row r="42" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A42" s="29" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 37: Mở Calendar Accepted → Chọn chuyến bay cần điều chỉnh → Nhấn F8 → Hệ thống cho phép kéo-thả hoặc nhập vị trí dòng mới → Lưu dữ liệu hiển thị theo user/session → Hiển thị lại lịch với bố cục mới</t>
-        </is>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D42" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 37</t>
-        </is>
-      </c>
-      <c r="E42" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 37.
-2. Thực hiện chuỗi nghiệp vụ: Mở Calendar Accepted → Chọn chuyến bay cần điều chỉnh → Nhấn F8 → Hệ thống cho phép kéo-thả hoặc nhập vị trí dòng mới → Lưu dữ liệu hiển thị theo user/session → Hiển thị lại lịch với bố cục mới.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F42" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 37, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
+    <row r="42" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A42" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
       <c r="Q42" s="1"/>
     </row>
-    <row r="43" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A43" s="29" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 38: Vị trí mới trùng với chuyến khác → Cảnh báo và yêu cầu chọn vị trí khác</t>
-        </is>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D43" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 38</t>
-        </is>
-      </c>
-      <c r="E43" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 38.
-2. Thực hiện chuỗi nghiệp vụ: Vị trí mới trùng với chuyến khác → Cảnh báo và yêu cầu chọn vị trí khác.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 38, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
+    <row r="43" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A43" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="F43" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
       <c r="Q43" s="1"/>
     </row>
-    <row r="44" spans="1:17" ht="102" x14ac:dyDescent="0.2">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 39: Đến giờ quy định → Tạo kế hoạch bay → Hệ thống thực hiện → Ghi log → Hoàn thành toàn bộ trong &lt; 60s → Gửi thông báo "Gen KHB completed"</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D44" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 39</t>
-        </is>
-      </c>
-      <c r="E44" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 39.
-2. Thực hiện chuỗi nghiệp vụ: Đến giờ quy định → Tạo kế hoạch bay → Hệ thống thực hiện → Ghi log → Hoàn thành toàn bộ trong &lt; 60s → Gửi thông báo "Gen KHB completed".
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F44" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 39, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
+    <row r="44" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A44" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="26"/>
       <c r="Q44" s="1"/>
     </row>
-    <row r="45" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 40: Lỗi kết nối AMHS → Lưu messages vào local queue. retry tự động khi kết nối phục hồi</t>
-        </is>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D45" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 40</t>
-        </is>
-      </c>
-      <c r="E45" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 40.
-2. Thực hiện chuỗi nghiệp vụ: Lỗi kết nối AMHS → Lưu messages vào local queue. retry tự động khi kết nối phục hồi.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 40, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="40"/>
-      <c r="N45" s="28"/>
-      <c r="O45" s="27"/>
-      <c r="P45" s="27"/>
+    <row r="45" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A45" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="36"/>
+      <c r="N45" s="26"/>
+      <c r="O45" s="25"/>
+      <c r="P45" s="25"/>
       <c r="Q45" s="1"/>
     </row>
-    <row r="46" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A46" s="29" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 41: Vào mục INBOX → Chọn date range: từ [date] đến [date] (tối đa 60 ngày) → Hệ thống query cả bảng current + archive → Hiển thị kết quả với pagination → Cho phép export kết quả tìm kiếm</t>
-        </is>
-      </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D46" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 41</t>
-        </is>
-      </c>
-      <c r="E46" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 41.
-2. Thực hiện chuỗi nghiệp vụ: Vào mục INBOX → Chọn date range: từ [date] đến [date] (tối đa 60 ngày) → Hệ thống query cả bảng current + archive → Hiển thị kết quả với pagination → Cho phép export kết quả tìm kiếm.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F46" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 41, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
+    <row r="46" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="26"/>
       <c r="Q46" s="1"/>
     </row>
-    <row r="47" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A47" s="29" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B47" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 42: Date range &gt; 60 ngày → Cảnh báo và yêu cầu thu hẹp. hoặc chuyển sang request báo cáo đặc biệt</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D47" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 42</t>
-        </is>
-      </c>
-      <c r="E47" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 42.
-2. Thực hiện chuỗi nghiệp vụ: Date range &gt; 60 ngày → Cảnh báo và yêu cầu thu hẹp. hoặc chuyển sang request báo cáo đặc biệt.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F47" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 42, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
-      <c r="M47" s="28"/>
-      <c r="N47" s="28"/>
-      <c r="O47" s="28"/>
-      <c r="P47" s="28"/>
+    <row r="47" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A47" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="F47" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="26"/>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="26"/>
+      <c r="O47" s="26"/>
+      <c r="P47" s="26"/>
       <c r="Q47" s="1"/>
     </row>
-    <row r="48" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A48" s="35" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B48" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 43: Phát hiện edit request trên KHB đã build → Hệ thống kiểm tra → Cập nhật chỉ số → UI luôn hiển thị bản mới nhất. có toggle xem history → Ghi audit log thay đổi version</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D48" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 43</t>
-        </is>
-      </c>
-      <c r="E48" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 43.
-2. Thực hiện chuỗi nghiệp vụ: Phát hiện edit request trên KHB đã build → Hệ thống kiểm tra → Cập nhật chỉ số → UI luôn hiển thị bản mới nhất. có toggle xem history → Ghi audit log thay đổi version.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F48" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 43, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
-      <c r="M48" s="28"/>
-      <c r="N48" s="28"/>
-      <c r="O48" s="28"/>
-      <c r="P48" s="28"/>
+    <row r="48" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E48" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="F48" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="26"/>
       <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="29" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 44: Người dùng muốn giữ cả 2 version → Cho phép clone thành flight mới với ID khác. không ghi đè \n36</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D49" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 44</t>
-        </is>
-      </c>
-      <c r="E49" s="37" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 44.
-2. Thực hiện chuỗi nghiệp vụ: Người dùng muốn giữ cả 2 version → Cho phép clone thành flight mới với ID khác. không ghi đè \n36.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F49" s="37" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 44, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
+    <row r="49" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A49" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="26"/>
+      <c r="O49" s="26"/>
+      <c r="P49" s="26"/>
       <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:17" ht="102" x14ac:dyDescent="0.2">
-      <c r="A50" s="29" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B50" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 45: Khi nhập/cập nhật permit → Tính toán ghi log</t>
-        </is>
-      </c>
-      <c r="C50" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D50" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 45</t>
-        </is>
-      </c>
-      <c r="E50" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 45.
-2. Thực hiện chuỗi nghiệp vụ: Khi nhập/cập nhật permit → Tính toán ghi log.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F50" s="37" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 45, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G50" s="28"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="28"/>
-      <c r="J50" s="28"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
-      <c r="M50" s="28"/>
-      <c r="N50" s="28"/>
-      <c r="O50" s="28"/>
-      <c r="P50" s="28"/>
+    <row r="50" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A50" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="E50" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="26"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="26"/>
+      <c r="O50" s="26"/>
+      <c r="P50" s="26"/>
       <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A51" s="29" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B51" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 46: Sai lệch do múi giờ hoặc chuyển ngày dương lịch → Hệ thống hỗ trợ convert timezone trước khi so sánh</t>
-        </is>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D51" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 46</t>
-        </is>
-      </c>
-      <c r="E51" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 46.
-2. Thực hiện chuỗi nghiệp vụ: Sai lệch do múi giờ hoặc chuyển ngày dương lịch → Hệ thống hỗ trợ convert timezone trước khi so sánh.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F51" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 46, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
+    <row r="51" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A51" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="26"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="26"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="26"/>
+      <c r="O51" s="26"/>
+      <c r="P51" s="26"/>
       <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A52" s="29" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 47: Khi thực hiện tạo điện văn → Bổ sung mục đích (Purpose) vào thông tin điện văn được sinh ra</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D52" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 47</t>
-        </is>
-      </c>
-      <c r="E52" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 47.
-2. Thực hiện chuỗi nghiệp vụ: Khi thực hiện tạo điện văn → Bổ sung mục đích (Purpose) vào thông tin điện văn được sinh ra.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F52" s="37" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 47, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
+    <row r="52" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A52" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="B52" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+      <c r="K52" s="26"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="26"/>
+      <c r="O52" s="26"/>
+      <c r="P52" s="26"/>
       <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A53" s="29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B53" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 48: Mục đích không có trong danh sách → Cho phép nhập custom với quyền admin. đề xuất thêm vào danh sách chuẩn</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D53" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 48</t>
-        </is>
-      </c>
-      <c r="E53" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 48.
-2. Thực hiện chuỗi nghiệp vụ: Mục đích không có trong danh sách → Cho phép nhập custom với quyền admin. đề xuất thêm vào danh sách chuẩn.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F53" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 48, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
+    <row r="53" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A53" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="26"/>
+      <c r="K53" s="26"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="26"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="26"/>
       <c r="Q53" s="1"/>
     </row>
-    <row r="54" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B54" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 49: Tại màn hình cập nhật phép bay → Kiểm tra ngày hiệu lực → Hiện thị "đỏ" để cảnh báo</t>
-        </is>
-      </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D54" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 49</t>
-        </is>
-      </c>
-      <c r="E54" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 49.
-2. Thực hiện chuỗi nghiệp vụ: Tại màn hình cập nhật phép bay → Kiểm tra ngày hiệu lực → Hiện thị "đỏ" để cảnh báo.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 49, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
-      <c r="M54" s="28"/>
-      <c r="N54" s="28"/>
-      <c r="O54" s="28"/>
-      <c r="P54" s="28"/>
+    <row r="54" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A54" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="F54" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="26"/>
+      <c r="O54" s="26"/>
+      <c r="P54" s="26"/>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A55" s="29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B55" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 50: Khi nhận chuyến bay từ TBHĐB → Tự động kiểm tra và cập nhật đường bay dựa trên FPL thực tế đã nộp</t>
-        </is>
-      </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D55" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 50</t>
-        </is>
-      </c>
-      <c r="E55" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 50.
-2. Thực hiện chuỗi nghiệp vụ: Khi nhận chuyến bay từ TBHĐB → Tự động kiểm tra và cập nhật đường bay dựa trên FPL thực tế đã nộp.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F55" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 50, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
+    <row r="55" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A55" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="F55" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="26"/>
+      <c r="O55" s="25"/>
+      <c r="P55" s="25"/>
       <c r="Q55" s="1"/>
     </row>
-    <row r="56" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A56" s="35" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B56" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 51: Route string không chuẩn → đánh flag ROUTE_UNCERTAIN để kiểm tra thủ công</t>
-        </is>
-      </c>
-      <c r="C56" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 51</t>
-        </is>
-      </c>
-      <c r="E56" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 51.
-2. Thực hiện chuỗi nghiệp vụ: Route string không chuẩn → đánh flag ROUTE_UNCERTAIN để kiểm tra thủ công.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 51, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G56" s="28"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
-      <c r="J56" s="28"/>
-      <c r="K56" s="28"/>
-      <c r="L56" s="28"/>
-      <c r="M56" s="28"/>
-      <c r="N56" s="28"/>
-      <c r="O56" s="28"/>
-      <c r="P56" s="28"/>
+    <row r="56" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A56" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="F56" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="26"/>
+      <c r="O56" s="26"/>
+      <c r="P56" s="26"/>
       <c r="Q56" s="1"/>
     </row>
-    <row r="57" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A57" s="29" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B57" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 52: Export từ danh sách chuyến bay sau khi khai thác xong → Tự động kiểm tra và đánh dấu chuyến bay chuyển ngày</t>
-        </is>
-      </c>
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D57" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 52</t>
-        </is>
-      </c>
-      <c r="E57" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 52.
-2. Thực hiện chuỗi nghiệp vụ: Export từ danh sách chuyến bay sau khi khai thác xong → Tự động kiểm tra và đánh dấu chuyến bay chuyển ngày.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 52, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
-      <c r="N57" s="28"/>
-      <c r="O57" s="28"/>
-      <c r="P57" s="28"/>
+    <row r="57" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="E57" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F57" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="26"/>
       <c r="Q57" s="1"/>
     </row>
-    <row r="58" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A58" s="29" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B58" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 53: Mở màn hình Daily Plan → Hệ thống load baseline KHBN → Khi có chuyến bay mới được thêm: hiển thị badge "NEW". highlight row → Counter hiển thị: +X flights added → Cho phép filter → Audit log ghi nhận</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D58" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 53</t>
-        </is>
-      </c>
-      <c r="E58" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 53.
-2. Thực hiện chuỗi nghiệp vụ: Mở màn hình Daily Plan → Hệ thống load baseline KHBN → Khi có chuyến bay mới được thêm: hiển thị badge "NEW". highlight row → Counter hiển thị: +X flights added → Cho phép filter → Audit log ghi nhận.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 53, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
+    <row r="58" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A58" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D58" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="F58" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="26"/>
+      <c r="O58" s="26"/>
+      <c r="P58" s="26"/>
       <c r="Q58" s="1"/>
     </row>
-    <row r="59" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A59" s="29" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B59" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 54: Hệ thống nhận dữ liệu từ Trung tâm TBHĐB → Hiển thị thông báo trên Dashboard → Cho phép click để xem chi tiết danh sách chuyến vừa cập nhật → Ghi log</t>
-        </is>
-      </c>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D59" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 54</t>
-        </is>
-      </c>
-      <c r="E59" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 54.
-2. Thực hiện chuỗi nghiệp vụ: Hệ thống nhận dữ liệu từ Trung tâm TBHĐB → Hiển thị thông báo trên Dashboard → Cho phép click để xem chi tiết danh sách chuyến vừa cập nhật → Ghi log.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 54, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="30"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="28"/>
-      <c r="O59" s="27"/>
-      <c r="P59" s="27"/>
+    <row r="59" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="F59" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="26"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="25"/>
+      <c r="N59" s="26"/>
+      <c r="O59" s="25"/>
+      <c r="P59" s="25"/>
       <c r="Q59" s="1"/>
     </row>
-    <row r="60" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A60" s="29" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B60" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 55: Chức năng đồng bộ sang Bravo → Với mỗi chuyến bay kiểm tra → Nếu tồn tại: UPDATE chỉ các trường thay đổi. KEEP ORIGINAL → Nếu \n37 không tồn tại: INSERT new record → Ghi log sync result → Gửi notification khi hoàn thành</t>
-        </is>
-      </c>
-      <c r="C60" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D60" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 55</t>
-        </is>
-      </c>
-      <c r="E60" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 55.
-2. Thực hiện chuỗi nghiệp vụ: Chức năng đồng bộ sang Bravo → Với mỗi chuyến bay kiểm tra → Nếu tồn tại: UPDATE chỉ các trường thay đổi. KEEP ORIGINAL → Nếu \n37 không tồn tại: INSERT new record → Ghi log sync result → Gửi notification khi hoàn thành.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 55, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="28"/>
-      <c r="M60" s="28"/>
-      <c r="N60" s="28"/>
-      <c r="O60" s="28"/>
-      <c r="P60" s="28"/>
+    <row r="60" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A60" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="F60" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="26"/>
+      <c r="O60" s="26"/>
+      <c r="P60" s="26"/>
       <c r="Q60" s="1"/>
     </row>
-    <row r="61" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A61" s="29" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B61" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 56: Xung đột dữ liệu (Bravo đã sửa manual) → Áp dụng policy manual_override_wins hoặc đưa vào conflict queue để review</t>
-        </is>
-      </c>
-      <c r="C61" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D61" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 56</t>
-        </is>
-      </c>
-      <c r="E61" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 56.
-2. Thực hiện chuỗi nghiệp vụ: Xung đột dữ liệu (Bravo đã sửa manual) → Áp dụng policy manual_override_wins hoặc đưa vào conflict queue để review.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 56, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
+    <row r="61" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="F61" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
       <c r="Q61" s="1"/>
     </row>
-    <row r="62" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A62" s="29" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B62" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 57: Khi nhận chuyến bay từ TBHĐB → Kiểm tra ngày → Cập nhật đúng ngày thực tế</t>
-        </is>
-      </c>
-      <c r="C62" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D62" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 57</t>
-        </is>
-      </c>
-      <c r="E62" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 57.
-2. Thực hiện chuỗi nghiệp vụ: Khi nhận chuyến bay từ TBHĐB → Kiểm tra ngày → Cập nhật đúng ngày thực tế.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F62" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 57, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="28"/>
-      <c r="J62" s="28"/>
-      <c r="K62" s="28"/>
-      <c r="L62" s="28"/>
-      <c r="M62" s="28"/>
-      <c r="N62" s="28"/>
-      <c r="O62" s="28"/>
-      <c r="P62" s="28"/>
+    <row r="62" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A62" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="B62" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="F62" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="26"/>
+      <c r="L62" s="26"/>
+      <c r="M62" s="26"/>
+      <c r="N62" s="26"/>
+      <c r="O62" s="26"/>
+      <c r="P62" s="26"/>
       <c r="Q62" s="1"/>
     </row>
-    <row r="63" spans="1:17" ht="102" x14ac:dyDescent="0.2">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B63" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 58: Trên danh sách chuyến bay. chọn nhiều dòng → Chọn field cần sửa → Nhập giá trị mới → Preview changes → Confirm → Hệ thống thực hiện batch update với transaction → Hiển thị kết quả → Ghi log cho từng chuyến bay</t>
-        </is>
-      </c>
-      <c r="C63" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D63" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 58</t>
-        </is>
-      </c>
-      <c r="E63" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 58.
-2. Thực hiện chuỗi nghiệp vụ: Trên danh sách chuyến bay. chọn nhiều dòng → Chọn field cần sửa → Nhập giá trị mới → Preview changes → Confirm → Hệ thống thực hiện batch update với transaction → Hiển thị kết quả → Ghi log cho từng chuyến bay.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 58, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G63" s="28"/>
-      <c r="H63" s="28"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="28"/>
-      <c r="K63" s="28"/>
-      <c r="L63" s="28"/>
-      <c r="M63" s="28"/>
-      <c r="N63" s="28"/>
-      <c r="O63" s="28"/>
-      <c r="P63" s="28"/>
+    <row r="63" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A63" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B63" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="E63" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="F63" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="26"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="26"/>
       <c r="Q63" s="1"/>
     </row>
-    <row r="64" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A64" s="29" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B64" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 59: Một số flight không đủ quyền sửa → Bỏ qua những flight đó. cập nhật những flight hợp lệ. báo cáo chi tiết</t>
-        </is>
-      </c>
-      <c r="C64" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D64" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 59</t>
-        </is>
-      </c>
-      <c r="E64" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 59.
-2. Thực hiện chuỗi nghiệp vụ: Một số flight không đủ quyền sửa → Bỏ qua những flight đó. cập nhật những flight hợp lệ. báo cáo chi tiết.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F64" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 59, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="28"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
+    <row r="64" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A64" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="B64" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="F64" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="26"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="25"/>
+      <c r="N64" s="26"/>
+      <c r="O64" s="25"/>
+      <c r="P64" s="25"/>
       <c r="Q64" s="1"/>
     </row>
-    <row r="65" spans="1:17" ht="102" x14ac:dyDescent="0.2">
-      <c r="A65" s="29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B65" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 60: Chọn phạm vi đối chiếu → Hệ thống fetch data từ cả 2 nguồn → Match records → So sánh fields → Highlight mismatches → Sinh báo cáo đối chiếu → Cho phép export discrepancy list để xử lý</t>
-        </is>
-      </c>
-      <c r="C65" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D65" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 60</t>
-        </is>
-      </c>
-      <c r="E65" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 60.
-2. Thực hiện chuỗi nghiệp vụ: Chọn phạm vi đối chiếu → Hệ thống fetch data từ cả 2 nguồn → Match records → So sánh fields → Highlight mismatches → Sinh báo cáo đối chiếu → Cho phép export discrepancy list để xử lý.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 60, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G65" s="28"/>
-      <c r="H65" s="28"/>
-      <c r="I65" s="28"/>
-      <c r="J65" s="28"/>
-      <c r="K65" s="28"/>
-      <c r="L65" s="28"/>
-      <c r="M65" s="28"/>
-      <c r="N65" s="28"/>
-      <c r="O65" s="28"/>
-      <c r="P65" s="28"/>
+    <row r="65" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A65" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="B65" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="C65" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+      <c r="K65" s="26"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="26"/>
       <c r="Q65" s="1"/>
     </row>
-    <row r="66" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A66" s="35" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B66" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 61: Không tìm thấy match key → Đánh dấu ORPHAN ở cả 2 phía. đề xuất kiểm tra dữ liệu nguồn</t>
-        </is>
-      </c>
-      <c r="C66" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D66" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 61</t>
-        </is>
-      </c>
-      <c r="E66" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 61.
-2. Thực hiện chuỗi nghiệp vụ: Không tìm thấy match key → Đánh dấu ORPHAN ở cả 2 phía. đề xuất kiểm tra dữ liệu nguồn.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F66" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 61, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="28"/>
-      <c r="J66" s="28"/>
-      <c r="K66" s="28"/>
-      <c r="L66" s="28"/>
-      <c r="M66" s="28"/>
-      <c r="N66" s="28"/>
-      <c r="O66" s="28"/>
-      <c r="P66" s="28"/>
+    <row r="66" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A66" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="C66" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="F66" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+      <c r="K66" s="26"/>
+      <c r="L66" s="26"/>
+      <c r="M66" s="26"/>
+      <c r="N66" s="26"/>
+      <c r="O66" s="26"/>
+      <c r="P66" s="26"/>
       <c r="Q66" s="1"/>
     </row>
-    <row r="67" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B67" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 62: Mở Daily Military Report → Click vào search bar → Nhập từ khóa hoặc chọn field-specific filter → Hệ thống query với full-text search → Hiển thị kết quả với highlight match → Cho phép save search criteria → Export kết quả</t>
-        </is>
-      </c>
-      <c r="C67" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D67" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 62</t>
-        </is>
-      </c>
-      <c r="E67" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 62.
-2. Thực hiện chuỗi nghiệp vụ: Mở Daily Military Report → Click vào search bar → Nhập từ khóa hoặc chọn field-specific filter → Hệ thống query với full-text search → Hiển thị kết quả với highlight match → Cho phép save search criteria → Export kết quả.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 62, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28"/>
-      <c r="P67" s="28"/>
+    <row r="67" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A67" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="B67" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" s="33" t="s">
+        <v>337</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="F67" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="26"/>
+      <c r="K67" s="26"/>
+      <c r="L67" s="26"/>
+      <c r="M67" s="26"/>
+      <c r="N67" s="26"/>
+      <c r="O67" s="26"/>
+      <c r="P67" s="26"/>
       <c r="Q67" s="1"/>
     </row>
-    <row r="68" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B68" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 63: Mở bất kỳ báo cáo nào → Hiển thị panel filters với tất cả criteria → Người dùng chọn/combine nhiều criteria → Hệ thống build dynamic query → Hiển thị kết quả với option show/hide columns → Cho phép save filter \n38 preset → Export</t>
-        </is>
-      </c>
-      <c r="C68" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 3: NÂNG CẤP VÀ TỐI ƯU CÁC CHỨC NĂNG CỦA HTSLB; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D68" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 63</t>
-        </is>
-      </c>
-      <c r="E68" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 63.
-2. Thực hiện chuỗi nghiệp vụ: Mở bất kỳ báo cáo nào → Hiển thị panel filters với tất cả criteria → Người dùng chọn/combine nhiều criteria → Hệ thống build dynamic query → Hiển thị kết quả với option show/hide columns → Cho phép save filter \n38 preset → Export.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F68" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 63, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G68" s="28"/>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28"/>
-      <c r="J68" s="28"/>
-      <c r="K68" s="28"/>
-      <c r="L68" s="28"/>
-      <c r="M68" s="28"/>
-      <c r="N68" s="28"/>
-      <c r="O68" s="28"/>
-      <c r="P68" s="28"/>
+    <row r="68" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A68" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="B68" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="E68" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="F68" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+      <c r="K68" s="26"/>
+      <c r="L68" s="26"/>
+      <c r="M68" s="26"/>
+      <c r="N68" s="26"/>
+      <c r="O68" s="26"/>
+      <c r="P68" s="26"/>
       <c r="Q68" s="1"/>
     </row>
-    <row r="69" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B69" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 64: Người dùng truy cập Dashboard → Hệ thống hiện thị: tổng chuyến bay. tỷ lệ on-time. delay distribution. airport heatmap → Dữ liệu auto-refresh → Cho phép click để xem chi tiết → Hỗ trợ tùy chỉnh layout</t>
-        </is>
-      </c>
-      <c r="C69" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D69" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 64</t>
-        </is>
-      </c>
-      <c r="E69" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 64.
-2. Thực hiện chuỗi nghiệp vụ: Người dùng truy cập Dashboard → Hệ thống hiện thị: tổng chuyến bay. tỷ lệ on-time. delay distribution. airport heatmap → Dữ liệu auto-refresh → Cho phép click để xem chi tiết → Hỗ trợ tùy chỉnh layout.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 64, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="28"/>
-      <c r="K69" s="28"/>
-      <c r="L69" s="28"/>
-      <c r="M69" s="27"/>
-      <c r="N69" s="28"/>
-      <c r="O69" s="27"/>
-      <c r="P69" s="28"/>
+    <row r="69" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A69" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="B69" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="C69" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D69" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="F69" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="25"/>
+      <c r="N69" s="26"/>
+      <c r="O69" s="25"/>
+      <c r="P69" s="26"/>
       <c r="Q69" s="1"/>
     </row>
-    <row r="70" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B70" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 65: Mất kết nối dữ liệu real-time → Hiển thị thông báo "Dữ liệu cập nhật lúc HH:mm"</t>
-        </is>
-      </c>
-      <c r="C70" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D70" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 65</t>
-        </is>
-      </c>
-      <c r="E70" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 65.
-2. Thực hiện chuỗi nghiệp vụ: Mất kết nối dữ liệu real-time → Hiển thị thông báo "Dữ liệu cập nhật lúc HH:mm".
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F70" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 65, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
+    <row r="70" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A70" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="B70" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="C70" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D70" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="F70" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="25"/>
+      <c r="N70" s="26"/>
+      <c r="O70" s="25"/>
+      <c r="P70" s="25"/>
       <c r="Q70" s="1"/>
     </row>
-    <row r="71" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B71" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 66: Chọn chỉ số phân tích → Chọn granularity → Hệ thống tính toán trend line. moving average. seasonality → Hiển thị biểu đồ với confidence interval → Dự báo ngắn hạn → Export kết quả phân tích</t>
-        </is>
-      </c>
-      <c r="C71" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D71" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 66</t>
-        </is>
-      </c>
-      <c r="E71" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 66.
-2. Thực hiện chuỗi nghiệp vụ: Chọn chỉ số phân tích → Chọn granularity → Hệ thống tính toán trend line. moving average. seasonality → Hiển thị biểu đồ với confidence interval → Dự báo ngắn hạn → Export kết quả phân tích.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 66, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G71" s="28"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="28"/>
-      <c r="J71" s="28"/>
-      <c r="K71" s="28"/>
-      <c r="L71" s="28"/>
-      <c r="M71" s="28"/>
-      <c r="N71" s="28"/>
-      <c r="O71" s="28"/>
-      <c r="P71" s="28"/>
+    <row r="71" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A71" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="B71" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="C71" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D71" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="E71" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="F71" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
       <c r="Q71" s="1"/>
     </row>
-    <row r="72" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A72" s="29" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B72" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 67: Engine giám sát luồng dữ liệu mới → So sánh với statistical baseline → Nếu giá trị vượt ngưỡng: đánh dấu ANOMALY → Phân loại nguyên nhân → Gửi alert → Ghi log để huấn luyện mô hình</t>
-        </is>
-      </c>
-      <c r="C72" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D72" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 67</t>
-        </is>
-      </c>
-      <c r="E72" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 67.
-2. Thực hiện chuỗi nghiệp vụ: Engine giám sát luồng dữ liệu mới → So sánh với statistical baseline → Nếu giá trị vượt ngưỡng: đánh dấu ANOMALY → Phân loại nguyên nhân → Gửi alert → Ghi log để huấn luyện mô hình.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F72" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 67, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G72" s="28"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="28"/>
-      <c r="J72" s="28"/>
-      <c r="K72" s="28"/>
-      <c r="L72" s="28"/>
-      <c r="M72" s="28"/>
-      <c r="N72" s="28"/>
-      <c r="O72" s="28"/>
-      <c r="P72" s="28"/>
+    <row r="72" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A72" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="B72" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D72" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="E72" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="F72" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="26"/>
       <c r="Q72" s="1"/>
     </row>
-    <row r="73" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A73" s="29" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B73" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 68: Bất thường được xác nhận là hợp lệ → Đánh dấu VALIDATED. cập nhật baseline để không cảnh báo lặp</t>
-        </is>
-      </c>
-      <c r="C73" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu vào</t>
-        </is>
-      </c>
-      <c r="D73" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 68</t>
-        </is>
-      </c>
-      <c r="E73" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 68.
-2. Thực hiện chuỗi nghiệp vụ: Bất thường được xác nhận là hợp lệ → Đánh dấu VALIDATED. cập nhật baseline để không cảnh báo lặp.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 68, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G73" s="28"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="28"/>
-      <c r="J73" s="28"/>
-      <c r="K73" s="28"/>
-      <c r="L73" s="28"/>
-      <c r="M73" s="28"/>
-      <c r="N73" s="28"/>
-      <c r="O73" s="28"/>
-      <c r="P73" s="28"/>
+    <row r="73" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A73" s="27" t="s">
+        <v>366</v>
+      </c>
+      <c r="B73" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="C73" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="D73" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="E73" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="F73" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="26"/>
       <c r="Q73" s="1"/>
     </row>
-    <row r="74" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A74" s="29" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B74" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 69: Người dùng chọn tiêu chí báo cáo O/F → Hệ thống query ADS-B tracks đã correlate → Tính toán metrics → So sánh với planned values → Sinh báo cáo dạng bảng + biểu đồ → Export PDF/Excel/CSV</t>
-        </is>
-      </c>
-      <c r="C74" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D74" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 69</t>
-        </is>
-      </c>
-      <c r="E74" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 69.
-2. Thực hiện chuỗi nghiệp vụ: Người dùng chọn tiêu chí báo cáo O/F → Hệ thống query ADS-B tracks đã correlate → Tính toán metrics → So sánh với planned values → Sinh báo cáo dạng bảng + biểu đồ → Export PDF/Excel/CSV.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 69, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G74" s="28"/>
-      <c r="H74" s="28"/>
-      <c r="I74" s="28"/>
-      <c r="J74" s="28"/>
-      <c r="K74" s="28"/>
-      <c r="L74" s="28"/>
-      <c r="M74" s="28"/>
-      <c r="N74" s="28"/>
-      <c r="O74" s="28"/>
-      <c r="P74" s="28"/>
+    <row r="74" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A74" s="27" t="s">
+        <v>372</v>
+      </c>
+      <c r="B74" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="C74" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D74" s="33" t="s">
+        <v>374</v>
+      </c>
+      <c r="E74" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="F74" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
+      <c r="N74" s="26"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="26"/>
       <c r="Q74" s="1"/>
     </row>
-    <row r="75" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B75" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 70: Thiếu dữ liệu ADS-B cho một số chuyến → Đánh dấu PARTIAL_DATA. hiển thị cảnh báo và vẫn báo cáo với dữ liệu có sẵn</t>
-        </is>
-      </c>
-      <c r="C75" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D75" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 70</t>
-        </is>
-      </c>
-      <c r="E75" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 70.
-2. Thực hiện chuỗi nghiệp vụ: Thiếu dữ liệu ADS-B cho một số chuyến → Đánh dấu PARTIAL_DATA. hiển thị cảnh báo và vẫn báo cáo với dữ liệu có sẵn.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 70, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G75" s="28"/>
-      <c r="H75" s="28"/>
-      <c r="I75" s="28"/>
-      <c r="J75" s="28"/>
-      <c r="K75" s="28"/>
-      <c r="L75" s="28"/>
-      <c r="M75" s="27"/>
-      <c r="N75" s="28"/>
-      <c r="O75" s="27"/>
-      <c r="P75" s="27"/>
+    <row r="75" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A75" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="B75" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="C75" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D75" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="E75" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="F75" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="25"/>
+      <c r="N75" s="26"/>
+      <c r="O75" s="25"/>
+      <c r="P75" s="25"/>
       <c r="Q75" s="1"/>
     </row>
-    <row r="76" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A76" s="35" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B76" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 71: Chọn bộ KPIs → Hệ thống aggregate theo dimension → Tính toán benchmark → Hiển thị ranking. heatmap. trend comparison → Cho phép drill-down từ aggregate vào chi tiết từng chuyến</t>
-        </is>
-      </c>
-      <c r="C76" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D76" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 71</t>
-        </is>
-      </c>
-      <c r="E76" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 71.
-2. Thực hiện chuỗi nghiệp vụ: Chọn bộ KPIs → Hệ thống aggregate theo dimension → Tính toán benchmark → Hiển thị ranking. heatmap. trend comparison → Cho phép drill-down từ aggregate vào chi tiết từng chuyến.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F76" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 71, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G76" s="28"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="28"/>
-      <c r="J76" s="28"/>
-      <c r="K76" s="28"/>
-      <c r="L76" s="28"/>
-      <c r="M76" s="28"/>
-      <c r="N76" s="28"/>
-      <c r="O76" s="28"/>
-      <c r="P76" s="28"/>
+    <row r="76" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A76" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>347</v>
+      </c>
+      <c r="D76" s="24" t="s">
+        <v>384</v>
+      </c>
+      <c r="E76" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="F76" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
       <c r="Q76" s="1"/>
     </row>
-    <row r="77" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B77" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 72: Người dùng chọn phạm vi → Hệ thống aggregate → Tính tỷ lệ % → Hiển \n39 thị pie chart + bar chart kép → Cho phép toggle → Hover để xem chi tiết số liệu → Export hình ảnh hoặc dữ liệu</t>
-        </is>
-      </c>
-      <c r="C77" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D77" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 72</t>
-        </is>
-      </c>
-      <c r="E77" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 72.
-2. Thực hiện chuỗi nghiệp vụ: Người dùng chọn phạm vi → Hệ thống aggregate → Tính tỷ lệ % → Hiển \n39 thị pie chart + bar chart kép → Cho phép toggle → Hover để xem chi tiết số liệu → Export hình ảnh hoặc dữ liệu.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 72, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G77" s="30"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="28"/>
-      <c r="J77" s="28"/>
-      <c r="K77" s="28"/>
-      <c r="L77" s="28"/>
-      <c r="M77" s="28"/>
-      <c r="N77" s="28"/>
-      <c r="O77" s="28"/>
-      <c r="P77" s="28"/>
+    <row r="77" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A77" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="B77" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="C77" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D77" s="33" t="s">
+        <v>389</v>
+      </c>
+      <c r="E77" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="F77" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="G77" s="28"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
+      <c r="N77" s="26"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="26"/>
       <c r="Q77" s="1"/>
     </row>
-    <row r="78" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B78" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 73: Chọn nhóm sân bay so sánh → Chọn granularity thời gian → Chọn metrics → Hệ thống tính toán → Hiển thị grouped bar chart → Highlight sân bay có biến động → Export báo cáo so sánh</t>
-        </is>
-      </c>
-      <c r="C78" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D78" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 73</t>
-        </is>
-      </c>
-      <c r="E78" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 73.
-2. Thực hiện chuỗi nghiệp vụ: Chọn nhóm sân bay so sánh → Chọn granularity thời gian → Chọn metrics → Hệ thống tính toán → Hiển thị grouped bar chart → Highlight sân bay có biến động → Export báo cáo so sánh.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F78" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 73, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G78" s="30"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="28"/>
-      <c r="J78" s="28"/>
-      <c r="K78" s="28"/>
-      <c r="L78" s="28"/>
-      <c r="M78" s="28"/>
-      <c r="N78" s="28"/>
-      <c r="O78" s="28"/>
-      <c r="P78" s="28"/>
+    <row r="78" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A78" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="B78" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D78" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="E78" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="F78" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="G78" s="28"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26"/>
       <c r="Q78" s="1"/>
     </row>
-    <row r="79" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A79" s="29" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B79" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 74: Mở báo cáo Military Flight → Chọn criteria → Hệ thống aggregate → Hiển thị bảng + biểu đồ → Cho phép drill-down → Export PDF/Excel với watermark</t>
-        </is>
-      </c>
-      <c r="C79" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D79" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 74</t>
-        </is>
-      </c>
-      <c r="E79" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 74.
-2. Thực hiện chuỗi nghiệp vụ: Mở báo cáo Military Flight → Chọn criteria → Hệ thống aggregate → Hiển thị bảng + biểu đồ → Cho phép drill-down → Export PDF/Excel với watermark.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 74, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G79" s="30"/>
-      <c r="H79" s="28"/>
-      <c r="I79" s="28"/>
-      <c r="J79" s="28"/>
-      <c r="K79" s="28"/>
-      <c r="L79" s="28"/>
-      <c r="M79" s="28"/>
-      <c r="N79" s="28"/>
-      <c r="O79" s="28"/>
-      <c r="P79" s="28"/>
+    <row r="79" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A79" s="27" t="s">
+        <v>397</v>
+      </c>
+      <c r="B79" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="C79" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="E79" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F79" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="G79" s="28"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="26"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="26"/>
+      <c r="N79" s="26"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="26"/>
       <c r="Q79" s="1"/>
     </row>
-    <row r="80" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A80" s="29" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B80" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 75: Mở báo cáo Consolidated Airport Report → Chọn filters linh hoạt TỔNG HỢP SỐ LIỆU TỰ ĐỘNG</t>
-        </is>
-      </c>
-      <c r="C80" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 4: PHÂN TÍCH, BÁO CÁO THÔNG MINH; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D80" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 75</t>
-        </is>
-      </c>
-      <c r="E80" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 75.
-2. Thực hiện chuỗi nghiệp vụ: Mở báo cáo Consolidated Airport Report → Chọn filters linh hoạt TỔNG HỢP SỐ LIỆU TỰ ĐỘNG.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F80" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 75, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G80" s="30"/>
-      <c r="H80" s="28"/>
-      <c r="I80" s="28"/>
-      <c r="J80" s="28"/>
-      <c r="K80" s="28"/>
-      <c r="L80" s="28"/>
-      <c r="M80" s="28"/>
-      <c r="N80" s="28"/>
-      <c r="O80" s="28"/>
-      <c r="P80" s="28"/>
+    <row r="80" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A80" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="B80" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="E80" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="F80" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="G80" s="28"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
       <c r="Q80" s="1"/>
     </row>
-    <row r="81" spans="1:17" ht="102" x14ac:dyDescent="0.2">
-      <c r="A81" s="29" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B81" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 76: Người dùng nhập câu hỏi → Chatbot tokenize và phân tích cú pháp → Nhận diện intent + entities → Map sang query cấu trúc → Chuyển truy vấn sang module xử lý dữ liệu → Nhận kết quả và sinh câu trả lời tự nhiên → Hiển thị kèm formatted data</t>
-        </is>
-      </c>
-      <c r="C81" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D81" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 76</t>
-        </is>
-      </c>
-      <c r="E81" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 76.
-2. Thực hiện chuỗi nghiệp vụ: Người dùng nhập câu hỏi → Chatbot tokenize và phân tích cú pháp → Nhận diện intent + entities → Map sang query cấu trúc → Chuyển truy vấn sang module xử lý dữ liệu → Nhận kết quả và sinh câu trả lời tự nhiên → Hiển thị kèm formatted data.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F81" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 76, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G81" s="30"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="28"/>
-      <c r="J81" s="28"/>
-      <c r="K81" s="28"/>
-      <c r="L81" s="28"/>
-      <c r="M81" s="28"/>
-      <c r="N81" s="28"/>
-      <c r="O81" s="28"/>
-      <c r="P81" s="28"/>
+    <row r="81" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A81" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B81" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="C81" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="E81" s="25" t="s">
+        <v>411</v>
+      </c>
+      <c r="F81" s="25" t="s">
+        <v>412</v>
+      </c>
+      <c r="G81" s="28"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="26"/>
       <c r="Q81" s="1"/>
     </row>
-    <row r="82" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A82" s="29" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B82" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 77: Câu hỏi mơ hồ hoặc thiếu thông tin → Chatbot hỏi lại làm rõ hoặc đề xuất các lựa chọn phổ biến</t>
-        </is>
-      </c>
-      <c r="C82" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D82" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 77</t>
-        </is>
-      </c>
-      <c r="E82" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 77.
-2. Thực hiện chuỗi nghiệp vụ: Câu hỏi mơ hồ hoặc thiếu thông tin → Chatbot hỏi lại làm rõ hoặc đề xuất các lựa chọn phổ biến.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F82" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 77, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G82" s="30"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="28"/>
-      <c r="J82" s="28"/>
-      <c r="K82" s="28"/>
-      <c r="L82" s="28"/>
-      <c r="M82" s="28"/>
-      <c r="N82" s="28"/>
-      <c r="O82" s="28"/>
-      <c r="P82" s="28"/>
+    <row r="82" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+      <c r="A82" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="B82" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="D82" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="E82" s="25" t="s">
+        <v>417</v>
+      </c>
+      <c r="F82" s="25" t="s">
+        <v>418</v>
+      </c>
+      <c r="G82" s="28"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="26"/>
+      <c r="K82" s="26"/>
+      <c r="L82" s="26"/>
+      <c r="M82" s="26"/>
+      <c r="N82" s="26"/>
+      <c r="O82" s="26"/>
+      <c r="P82" s="26"/>
       <c r="Q82" s="1"/>
     </row>
-    <row r="83" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A83" s="29" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B83" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 78: Nhận query object → Query Builder sinh SQL/API call → Thực thi truy vấn → Nếu kết quả lớn: áp dụng aggregation → Format kết quả thành JSON → Chuyển sang module sinh câu trả lời</t>
-        </is>
-      </c>
-      <c r="C83" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D83" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 78</t>
-        </is>
-      </c>
-      <c r="E83" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 78.
-2. Thực hiện chuỗi nghiệp vụ: Nhận query object → Query Builder sinh SQL/API call → Thực thi truy vấn → Nếu kết quả lớn: áp dụng aggregation → Format kết quả thành JSON → Chuyển sang module sinh câu trả lời.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F83" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 78, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G83" s="30"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="28"/>
-      <c r="J83" s="28"/>
-      <c r="K83" s="28"/>
-      <c r="L83" s="28"/>
-      <c r="M83" s="27"/>
-      <c r="N83" s="28"/>
-      <c r="O83" s="27"/>
-      <c r="P83" s="27"/>
+    <row r="83" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+      <c r="A83" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="B83" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="D83" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="E83" s="25" t="s">
+        <v>422</v>
+      </c>
+      <c r="F83" s="25" t="s">
+        <v>423</v>
+      </c>
+      <c r="G83" s="28"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
+      <c r="J83" s="26"/>
+      <c r="K83" s="26"/>
+      <c r="L83" s="26"/>
+      <c r="M83" s="25"/>
+      <c r="N83" s="26"/>
+      <c r="O83" s="25"/>
+      <c r="P83" s="25"/>
       <c r="Q83" s="1"/>
     </row>
-    <row r="84" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A84" s="29" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B84" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 79: Truy vấn quá phức tạp hoặc tốn tài nguyên → Hệ thống đề xuất giới hạn phạm vi hoặc chạy background với notification khi hoàn thành</t>
-        </is>
-      </c>
-      <c r="C84" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D84" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 79</t>
-        </is>
-      </c>
-      <c r="E84" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 79.
-2. Thực hiện chuỗi nghiệp vụ: Truy vấn quá phức tạp hoặc tốn tài nguyên → Hệ thống đề xuất giới hạn phạm vi hoặc chạy background với notification khi hoàn thành.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F84" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 79, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G84" s="30"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="28"/>
-      <c r="J84" s="28"/>
-      <c r="K84" s="28"/>
-      <c r="L84" s="28"/>
-      <c r="M84" s="27"/>
-      <c r="N84" s="28"/>
-      <c r="O84" s="27"/>
-      <c r="P84" s="27"/>
+    <row r="84" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="B84" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="D84" s="33" t="s">
+        <v>426</v>
+      </c>
+      <c r="E84" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="F84" s="25" t="s">
+        <v>428</v>
+      </c>
+      <c r="G84" s="28"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="26"/>
+      <c r="K84" s="26"/>
+      <c r="L84" s="26"/>
+      <c r="M84" s="25"/>
+      <c r="N84" s="26"/>
+      <c r="O84" s="25"/>
+      <c r="P84" s="25"/>
       <c r="Q84" s="1"/>
     </row>
-    <row r="85" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A85" s="29" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B85" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 80: Thêm chat icon cố định ở góc màn hình → Khi click: mở chat panel → Hiển thị welcome message → Hỗ trợ input: text + voice + quick-reply \n40 buttons → Kết quả hiển thị trong chat → Hỗ trợ keyboard shortcut</t>
-        </is>
-      </c>
-      <c r="C85" s="26" t="inlineStr">
-        <is>
-          <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu vào/ra</t>
-        </is>
-      </c>
-      <c r="D85" s="37" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 80</t>
-        </is>
-      </c>
-      <c r="E85" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 80.
-2. Thực hiện chuỗi nghiệp vụ: Thêm chat icon cố định ở góc màn hình → Khi click: mở chat panel → Hiển thị welcome message → Hỗ trợ input: text + voice + quick-reply \n40 buttons → Kết quả hiển thị trong chat → Hỗ trợ keyboard shortcut.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F85" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 80, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G85" s="30"/>
-      <c r="H85" s="28"/>
-      <c r="I85" s="28"/>
-      <c r="J85" s="28"/>
-      <c r="K85" s="28"/>
-      <c r="L85" s="28"/>
-      <c r="M85" s="27"/>
-      <c r="N85" s="28"/>
-      <c r="O85" s="27"/>
-      <c r="P85" s="27"/>
+    <row r="85" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+      <c r="A85" s="27" t="s">
+        <v>429</v>
+      </c>
+      <c r="B85" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="C85" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="E85" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="F85" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="G85" s="28"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="26"/>
+      <c r="K85" s="26"/>
+      <c r="L85" s="26"/>
+      <c r="M85" s="25"/>
+      <c r="N85" s="26"/>
+      <c r="O85" s="25"/>
+      <c r="P85" s="25"/>
       <c r="Q85" s="1"/>
     </row>
-    <row r="86" spans="1:17" ht="51" x14ac:dyDescent="0.2">
-      <c r="A86" s="35" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B86" s="36" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 81: User đang làm việc với form quan trọng → Chatbot không auto-popup. chỉ hiển thị badge notification khi có alert quan trọng</t>
-        </is>
-      </c>
-      <c r="C86" s="37" t="inlineStr">
-        <is>
-          <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D86" s="26" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 81</t>
-        </is>
-      </c>
-      <c r="E86" s="27" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 81.
-2. Thực hiện chuỗi nghiệp vụ: User đang làm việc với form quan trọng → Chatbot không auto-popup. chỉ hiển thị badge notification khi có alert quan trọng.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F86" s="27" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 81, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
-      </c>
-      <c r="G86" s="28"/>
-      <c r="H86" s="28"/>
-      <c r="I86" s="28"/>
-      <c r="J86" s="28"/>
-      <c r="K86" s="28"/>
-      <c r="L86" s="28"/>
-      <c r="M86" s="28"/>
-      <c r="N86" s="28"/>
-      <c r="O86" s="28"/>
-      <c r="P86" s="28"/>
+    <row r="86" spans="1:17" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>435</v>
+      </c>
+      <c r="C86" s="33" t="s">
+        <v>415</v>
+      </c>
+      <c r="D86" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="E86" s="25" t="s">
+        <v>437</v>
+      </c>
+      <c r="F86" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="26"/>
+      <c r="J86" s="26"/>
+      <c r="K86" s="26"/>
+      <c r="L86" s="26"/>
+      <c r="M86" s="26"/>
+      <c r="N86" s="26"/>
+      <c r="O86" s="26"/>
+      <c r="P86" s="26"/>
       <c r="Q86" s="1"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87" s="12" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>Yêu cầu Bảng 1 số 82: Thu thập metrics: số câu hỏi/ngày. tỷ lệ các loại truy vấn. % query được xử lý đúng ngay lần đầu</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>NHÓM 5: ỨNG DỤNG AI HỖ TRỢ THỐNG KÊ, TÌM KIẾM VÀ TỔNG HỢP SỐ LIỆU TỰ ĐỘNG; Phân loại: Dữ liệu đầu ra</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>Kiểm thử yêu cầu Bảng 1 số 82</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị dữ liệu và quyền phù hợp cho yêu cầu số 82.
-2. Thực hiện chuỗi nghiệp vụ: Thu thập metrics: số câu hỏi/ngày. tỷ lệ các loại truy vấn. % query được xử lý đúng ngay lần đầu.
-3. Kiểm tra dữ liệu đầu vào/đầu ra, giao diện, trạng thái, hiệu năng và trường hợp lỗi; đối chiếu nhật ký kiểm toán.</t>
-        </is>
-      </c>
-      <c r="F87" s="10" t="inlineStr">
-        <is>
-          <t>Hệ thống thực hiện đúng yêu cầu số 82, tạo đầu ra/trạng thái theo mô tả; dữ liệu được kiểm tra nhất quán, lỗi được cảnh báo/xử lý an toàn, phân quyền được áp dụng và thao tác được ghi log.</t>
-        </is>
+    <row r="87" spans="1:17" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>443</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="5"/>
